--- a/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
+++ b/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>9066267.680703618</v>
+        <v>8938388.098683022</v>
       </c>
     </row>
     <row r="10">
@@ -539,13 +539,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>19891.47439593931</v>
+        <v>21041.50083063317</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>9086159.155099558</v>
+        <v>8959429.599513656</v>
       </c>
     </row>
     <row r="13">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>9066267.680703618</v>
+        <v>8938388.098683022</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-2608266.10095845</v>
+        <v>-2736145.682979046</v>
       </c>
     </row>
     <row r="16">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-9066267.680703618</v>
+        <v>-8938388.098683022</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>1225529.026659024</v>
+        <v>1353408.60867962</v>
       </c>
     </row>
     <row r="25">
@@ -666,7 +666,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-03T07:26:49+00:00</t>
+          <t>2026-07-07T01:10:59+00:00</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S62"/>
+  <dimension ref="A1:S64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -863,13 +863,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3234207.157498324</v>
+        <v>3189433.596046247</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3234207.157498324</v>
+        <v>3189433.596046247</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-207533.5862352524</v>
+        <v>-162760.0247831743</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -928,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1204563.374363613</v>
+        <v>1187887.697872096</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1204563.374363613</v>
+        <v>1187887.697872096</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>-106075.2052186128</v>
+        <v>-89399.52872709547</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -993,13 +993,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>948337.8823588227</v>
+        <v>935209.3280067354</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>948337.8823588227</v>
+        <v>935209.3280067354</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>48108.5374804059</v>
+        <v>61237.09183249316</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>156917846.5942976</v>
@@ -1062,13 +1062,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>927669.5167883105</v>
+        <v>914827.0901611712</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>927669.5167883105</v>
+        <v>914827.0901611712</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-927669.5167883642</v>
+        <v>-914827.0901612249</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1127,13 +1127,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>620914.7925401869</v>
+        <v>612319.0022068904</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>620914.7925401869</v>
+        <v>612319.0022068904</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>943730.2074598171</v>
+        <v>952325.9977931136</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1192,13 +1192,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>429285.5812760779</v>
+        <v>423342.6581985646</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>429285.5812760779</v>
+        <v>423342.6581985646</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>84517.72270958572</v>
+        <v>90460.64578709904</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>89993374.27336854</v>
@@ -1261,13 +1261,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>348528.0075993916</v>
+        <v>343703.0723351669</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>313132.1211247913</v>
+        <v>308307.1858605666</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>68344.1868955557</v>
+        <v>73169.12215978043</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1326,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>335556.805601552</v>
+        <v>330911.4404395117</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>301478.2514025327</v>
+        <v>296832.8862404924</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>55454.57133858281</v>
+        <v>60099.93650062312</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>304339.5414573538</v>
+        <v>300126.3403548375</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>273431.3572532926</v>
+        <v>269218.1561507764</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>45468.2275399581</v>
+        <v>49681.42864247441</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>254778.1558453507</v>
+        <v>251251.0702686146</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>254778.1558453507</v>
+        <v>251251.0702686146</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>160316.0273419627</v>
+        <v>163843.1129186988</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1521,13 +1521,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>242429.0009158371</v>
+        <v>239072.8739760071</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>242429.0009158371</v>
+        <v>239072.8739760071</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-215661.6619688371</v>
+        <v>-212305.5350290071</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1586,13 +1586,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>234344.4705104268</v>
+        <v>231100.2638036835</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>234344.4705104268</v>
+        <v>231100.2638036835</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-204218.3259900946</v>
+        <v>-200974.1192833513</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1712,13 +1712,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>47730.16149526071</v>
+        <v>47069.39698180923</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>47730.16149526071</v>
+        <v>47069.39698180923</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>47917.15819495428</v>
+        <v>48577.92270840576</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1777,13 +1777,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>29093.53646157885</v>
+        <v>28690.77276117681</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>29093.53646157885</v>
+        <v>28690.77276117681</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>8260.809913421152</v>
+        <v>8663.573613823188</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1842,13 +1842,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>27096.48169998937</v>
+        <v>26721.36473021926</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>27096.48169998937</v>
+        <v>26721.36473021926</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>17049.60626726576</v>
+        <v>17424.72323703587</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1976,13 +1976,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>10741.90149963542</v>
+        <v>10593.19328043831</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>9650.973029865294</v>
+        <v>9502.264810668192</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-7884.560076380619</v>
+        <v>-7735.851857183517</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2041,13 +2041,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>8482.987661560199</v>
+        <v>8365.551285080261</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>8482.987661560199</v>
+        <v>8365.551285080261</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-8482.987661560199</v>
+        <v>-8365.551285080261</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2106,13 +2106,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>8481.75638555295</v>
+        <v>8364.337054552565</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>8481.75638555295</v>
+        <v>8364.337054552565</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-8481.75638555289</v>
+        <v>-8364.337054552505</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2171,13 +2171,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>8432.375783650066</v>
+        <v>8315.640065450647</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>8432.375783650066</v>
+        <v>8315.640065450647</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-8432.375783635534</v>
+        <v>-8315.640065436115</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2236,13 +2236,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>8323.503023157531</v>
+        <v>8208.274512442043</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>8323.503023157531</v>
+        <v>8208.274512442043</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-8323.503023156936</v>
+        <v>-8208.274512441449</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2301,13 +2301,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3539.096277471609</v>
+        <v>3490.101906688395</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3539.096277471609</v>
+        <v>3490.101906688395</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1372.020064013611</v>
+        <v>1421.014434796825</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2320,124 +2320,128 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S61</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>Spark.fi PYUSD Reserve Uniswap V4 (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>424.9110349025811</v>
+        <v>220002.6507685304</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>394.3129623374141</v>
+        <v>100119969.930802</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-30.59807256516697</v>
+        <v>99899967.28003348</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>690.3378764287719</v>
+        <v>1030.276249266686</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>690.3378764287719</v>
+        <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0</v>
+        <v>1030.276249266686</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>193331.1163669253</v>
+        <v>22121073.51134836</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>468.6918988877537</v>
+        <v>0</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>468.6918988877537</v>
+        <v>1030.276249266686</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>221.6459775410182</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>0</v>
+        <v>22121073.51134836</v>
       </c>
       <c r="R25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>0</v>
+        <v>424.9110349025811</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0</v>
+        <v>394.3129623374141</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0</v>
+        <v>-30.59807256516697</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>3.15299999999996e-10</v>
+        <v>690.3378764287719</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>3.15299999999996e-10</v>
+        <v>690.3378764287719</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>1206.634682533317</v>
+        <v>193331.1163669253</v>
       </c>
       <c r="M26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2.925239926443179</v>
+        <v>462.2034445262915</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>2.925239926443179</v>
+        <v>462.2034445262915</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-2.925239926127879</v>
+        <v>228.1344319024803</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2450,12 +2454,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S62</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>Spark.fi USDT Reserve Uniswap V4 (USDT/USDS)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2465,109 +2469,113 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>539.8728953809741</v>
+        <v>1250066.267840007</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>637.4866706248019</v>
+        <v>50000000.01256605</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>97.6137752438278</v>
+        <v>48749933.74472605</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>97.6137752438278</v>
+        <v>119.7501854271759</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>97.6137752438278</v>
+        <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0</v>
+        <v>119.7501854271759</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>539.8728953809741</v>
+        <v>18435553.22634522</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>1.308811831479327</v>
+        <v>0</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.308811831479327</v>
+        <v>119.7501854271759</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>96.30496341234849</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>0</v>
+        <v>18435553.22634522</v>
       </c>
       <c r="R27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>0</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>0</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0</v>
+        <v>3.15299999999996e-10</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0</v>
+        <v>3.15299999999996e-10</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>1206.634682533317</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.6882510335376544</v>
+        <v>2.884743630680237</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6882510335376544</v>
+        <v>2.884743630680237</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-0.6882510335376544</v>
+        <v>-2.884743630364937</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2580,12 +2588,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2599,40 +2607,40 @@
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>99.81305763596731</v>
+        <v>539.8728953809741</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>100.1238263246728</v>
+        <v>637.4866706248019</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.3107686887055447</v>
+        <v>97.6137752438278</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.3107686887055447</v>
+        <v>97.6137752438278</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.3107686887055447</v>
+        <v>97.6137752438278</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>99.81305763596731</v>
+        <v>539.8728953809741</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.24197642053857</v>
+        <v>1.290692965212494</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.24197642053857</v>
+        <v>1.290692965212494</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.06879226816697472</v>
+        <v>96.32308227861532</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2645,17 +2653,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2664,40 +2672,40 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>21.90661272343654</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>21.90842102645718</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.001808303020639377</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.0001839966329158897</v>
+        <v>0</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.0001839966329158897</v>
+        <v>0</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>21.90693758471409</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.05310890646236246</v>
+        <v>0.6787230569907252</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.05310890646236246</v>
+        <v>0.6787230569907252</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-0.05292490982944657</v>
+        <v>-0.6787230569907252</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2710,12 +2718,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2725,44 +2733,44 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>10.015998</v>
+        <v>99.81305763596731</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1.353383</v>
+        <v>100.1238263246728</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-8.662615000000001</v>
+        <v>0.3107686887055447</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-8.662615000000001</v>
+        <v>0.3107686887055447</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>-8.662615000000001</v>
+        <v>0.3107686887055447</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>10.015998</v>
+        <v>99.81305763596731</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.02428174631219921</v>
+        <v>0.2386265590091936</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.02428174631219921</v>
+        <v>0.2386265590091936</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-8.686896746312199</v>
+        <v>0.07214212969635114</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2775,12 +2783,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2790,44 +2798,44 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>5.913258</v>
+        <v>21.90661272343654</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>5.924825</v>
+        <v>21.90842102645718</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.011567</v>
+        <v>0.001808303020639377</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.011567</v>
+        <v>0.0001839966329158897</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.011567</v>
+        <v>0.0001839966329158897</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>5.913258</v>
+        <v>21.90693758471409</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.0143354891479194</v>
+        <v>0.05237367993810216</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.0143354891479194</v>
+        <v>0.05237367993810216</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.002768489147919404</v>
+        <v>-0.05218968330518628</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2840,59 +2848,59 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0.155165</v>
+        <v>10.015998</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.155607</v>
+        <v>1.353383</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.000442</v>
+        <v>-8.662615000000001</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.000442</v>
+        <v>-8.662615000000001</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.000442</v>
+        <v>-8.662615000000001</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.155165</v>
+        <v>10.015998</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.0003761659264041776</v>
+        <v>0.02394559584077611</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.0003761659264041776</v>
+        <v>0.02394559584077611</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>6.583407359582241e-05</v>
+        <v>-8.686560595840776</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2905,12 +2913,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2924,40 +2932,40 @@
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0.057969</v>
+        <v>5.913258</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.058128</v>
+        <v>5.924825</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.000159</v>
+        <v>0.011567</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.000159</v>
+        <v>0.011567</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.000159</v>
+        <v>0.011567</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.057969</v>
+        <v>5.913258</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.0001405340288578208</v>
+        <v>0.01413703219292137</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.0001405340288578208</v>
+        <v>0.01413703219292137</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>1.846597114217916e-05</v>
+        <v>-0.002570032192921369</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2970,17 +2978,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2989,40 +2997,40 @@
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>0.006363</v>
+        <v>0.155165</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.006375</v>
+        <v>0.155607</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>1.2e-05</v>
+        <v>0.000442</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1.2e-05</v>
+        <v>0.000442</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>1.2e-05</v>
+        <v>0.000442</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.006363</v>
+        <v>0.155165</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>1.542579698843026e-05</v>
+        <v>0.0003709583786492394</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>1.542579698843026e-05</v>
+        <v>0.0003709583786492394</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-3.425796988430264e-06</v>
+        <v>7.104162135076057e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3035,12 +3043,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3054,40 +3062,40 @@
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.005746426914602806</v>
+        <v>0.057969</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.005747618663969358</v>
+        <v>0.058128</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>1.191749366552e-06</v>
+        <v>0.000159</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>1.191749366552e-06</v>
+        <v>0.000159</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>1.191749366552e-06</v>
+        <v>0.000159</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.005746426914602806</v>
+        <v>0.057969</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.393104117452689e-05</v>
+        <v>0.000138588510630089</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.393104117452689e-05</v>
+        <v>0.000138588510630089</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-1.273929180797489e-05</v>
+        <v>2.0411489369911e-05</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3100,17 +3108,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3119,40 +3127,40 @@
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>0.001705</v>
+        <v>0.006363</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.001709</v>
+        <v>0.006375</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>4e-06</v>
+        <v>1.2e-05</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>4e-06</v>
+        <v>1.2e-05</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>4e-06</v>
+        <v>1.2e-05</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.001705</v>
+        <v>0.006363</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>4.133425092766556e-06</v>
+        <v>1.521224608220353e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>4.133425092766556e-06</v>
+        <v>1.521224608220353e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.334250927665568e-07</v>
+        <v>-3.212246082203528e-06</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3165,12 +3173,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3180,44 +3188,44 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005746426914602806</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005747618663969358</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0</v>
+        <v>1.191749366552e-06</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0</v>
+        <v>1.191749366552e-06</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>0</v>
+        <v>1.191749366552e-06</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005746426914602806</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>3.006478064367456e-06</v>
+        <v>1.373818329692526e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>3.006478064367456e-06</v>
+        <v>1.373818329692526e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-3.006478064367456e-06</v>
+        <v>-1.254643393037326e-05</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3230,17 +3238,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3249,40 +3257,40 @@
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.000521673271312833</v>
+        <v>0.001705</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.000522139801452544</v>
+        <v>0.001709</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>4.66530139711e-07</v>
+        <v>4e-06</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>4.6653013971e-07</v>
+        <v>4e-06</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4.6653013971e-07</v>
+        <v>4e-06</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.000521673271312833</v>
+        <v>0.001705</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1.264690551243449e-06</v>
+        <v>4.076202981322807e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.264690551243449e-06</v>
+        <v>4.076202981322807e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-7.981604115334486e-07</v>
+        <v>-7.620298132280616e-08</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3295,12 +3303,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3310,14 +3318,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>0</v>
@@ -3335,19 +3343,19 @@
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.815707602057161e-07</v>
+        <v>2.964857127979014e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.815707602057161e-07</v>
+        <v>2.964857127979014e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-1.815707602057161e-07</v>
+        <v>-2.964857127979014e-06</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3360,12 +3368,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Maple syrupUSDT (ERC-4626)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3375,44 +3383,44 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0</v>
+        <v>0.000521673271312833</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0</v>
+        <v>0.000522139801452544</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0</v>
+        <v>4.66530139711e-07</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0</v>
+        <v>4.6653013971e-07</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0</v>
+        <v>4.6653013971e-07</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0</v>
+        <v>0.000521673271312833</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>0</v>
+        <v>1.247182489033309e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>0</v>
+        <v>1.247182489033309e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>0</v>
+        <v>-7.806523493233086e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3425,12 +3433,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3440,14 +3448,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
@@ -3465,19 +3473,19 @@
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0</v>
+        <v>1.790571396507918e-07</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0</v>
+        <v>1.790571396507918e-07</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0</v>
+        <v>-1.790571396507918e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3490,12 +3498,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>Maple syrupUSDT (ERC-4626)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3505,7 +3513,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
@@ -3555,12 +3563,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3598,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
         <v>0</v>
@@ -3615,21 +3623,17 @@
       <c r="R44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3689,12 +3693,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3704,7 +3708,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
@@ -3717,13 +3721,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>1435964.694856968</v>
+        <v>0</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>1435964.694856968</v>
+        <v>0</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0</v>
@@ -3732,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" s="6" t="n">
         <v>0</v>
@@ -3741,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>1435964.694856968</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="6" t="n">
         <v>0</v>
@@ -3749,17 +3753,21 @@
       <c r="R46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3769,7 +3777,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -3782,13 +3790,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>7.364216e-08</v>
+        <v>0</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>7.364216e-08</v>
+        <v>0</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0</v>
@@ -3806,7 +3814,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>7.364216e-08</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -3819,12 +3827,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3847,22 +3855,22 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-2.3626413e-07</v>
+        <v>1435964.694856968</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-2.3626413e-07</v>
+        <v>1435964.694856968</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>1925.254906924896</v>
+        <v>0</v>
       </c>
       <c r="M48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" s="6" t="n">
         <v>0</v>
@@ -3871,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>-2.3626413e-07</v>
+        <v>1435964.694856968</v>
       </c>
       <c r="Q48" s="6" t="n">
         <v>0</v>
@@ -3879,26 +3887,22 @@
       <c r="R48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
-        </is>
-      </c>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3907,31 +3911,31 @@
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>146550618.2104181</v>
+        <v>0</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>81380618.21041812</v>
+        <v>0</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>-2.524958539e-09</v>
+        <v>7.364216e-08</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>-2.524958539e-09</v>
+        <v>7.364216e-08</v>
       </c>
       <c r="K49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>95010226.6771533</v>
+        <v>0</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3940,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>-2.524958539e-09</v>
+        <v>7.364216e-08</v>
       </c>
       <c r="Q49" s="6" t="n">
         <v>0</v>
@@ -3948,31 +3952,27 @@
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
-        </is>
-      </c>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
@@ -3985,22 +3985,22 @@
         <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0</v>
+        <v>-2.3626413e-07</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0</v>
+        <v>-2.3626413e-07</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0</v>
+        <v>1925.254906924896</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50" s="6" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0</v>
+        <v>-2.3626413e-07</v>
       </c>
       <c r="Q50" s="6" t="n">
         <v>0</v>
@@ -4017,22 +4017,26 @@
       <c r="R50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4041,28 +4045,28 @@
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>90000000</v>
+        <v>146550618.2104181</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0</v>
+        <v>81380618.21041812</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>0</v>
+        <v>-2.524958539e-09</v>
       </c>
       <c r="I51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>0</v>
+        <v>-2.524958539e-09</v>
       </c>
       <c r="K51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>90000000</v>
+        <v>95010226.6771533</v>
       </c>
       <c r="M51" s="7" t="n">
         <v>0</v>
@@ -4074,67 +4078,67 @@
         <v>0</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0</v>
+        <v>-2.524958539e-09</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>90000000</v>
+        <v>0</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>100304256.5863323</v>
+        <v>0</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>10404256.58633234</v>
+        <v>0</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-1.484488714e-09</v>
+        <v>0</v>
       </c>
       <c r="I52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-1.484488714e-09</v>
+        <v>0</v>
       </c>
       <c r="K52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>93715560.74832186</v>
+        <v>0</v>
       </c>
       <c r="M52" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" s="6" t="n">
         <v>0</v>
@@ -4143,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>-1.484488714e-09</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
         <v>0</v>
@@ -4151,26 +4155,22 @@
       <c r="R52" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
-        </is>
-      </c>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>USDS raw (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4179,28 +4179,28 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>99990828.81481861</v>
+        <v>90000000</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>10090828.81481861</v>
+        <v>0</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-2.98022377e-10</v>
+        <v>0</v>
       </c>
       <c r="I53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>-2.98022377e-10</v>
+        <v>0</v>
       </c>
       <c r="K53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>93600637.23210016</v>
+        <v>90000000</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4212,185 +4212,267 @@
         <v>0</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>-2.98022377e-10</v>
+        <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+          <t>CoF excluded (already deducted from utilized)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>S48</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>USDS raw (Optimism — POL)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>optimism</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>100304256.5863323</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>10404256.58633234</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>-1.484488714e-09</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>-1.484488714e-09</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="6" t="n">
+        <v>93715560.74832186</v>
+      </c>
+      <c r="M54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v>-1.484488714e-09</v>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S52</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>USDS raw (Unichain — POL)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>unichain</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>99990828.81481861</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>10090828.81481861</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>-2.98022377e-10</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>-2.98022377e-10</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>93600637.23210016</v>
+      </c>
+      <c r="M55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v>-2.98022377e-10</v>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr">
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
         <is>
           <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>Position-only venues (PnL aggregated at prime level)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Pricing cat.</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Position SoM</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Position EoM</t>
         </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>S56</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>303545287.192935</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>317193040.533521</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>S57</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="n">
-        <v>1270360913.25412</v>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>863439216.480082</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
+          <t>Spark Savings V2 — spUSDC vault</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4404,51 +4486,107 @@
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>773533.783718</v>
+        <v>303545287.192935</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>797030.383413</v>
+        <v>317193040.533521</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDT vault</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>1270360913.25412</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>863439216.480082</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S59</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spPYUSD vault</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>773533.783718</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>797030.383413</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>S60</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>avalanche_c</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E63" s="6" t="n">
         <v>25647247.422478</v>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="F63" s="6" t="n">
         <v>19103797.28946</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" s="9" t="n">
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4503,7 +4641,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>2986217097.514784</v>
+        <v>2945662385.958665</v>
       </c>
     </row>
     <row r="6">
@@ -4523,7 +4661,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1986217097.514784</v>
+        <v>1945662385.958666</v>
       </c>
     </row>
     <row r="8">
@@ -4563,7 +4701,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.03835121139107078</v>
+        <v>0.03834079216689766</v>
       </c>
     </row>
     <row r="12">
@@ -4573,7 +4711,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-7.567928746118147</v>
+        <v>-7.67212098784927</v>
       </c>
     </row>
     <row r="13">
@@ -4593,7 +4731,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9416321.300288821</v>
+        <v>9288441.718268225</v>
       </c>
     </row>
     <row r="16">
@@ -4603,7 +4741,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9237350.035501989</v>
+        <v>9109470.453481393</v>
       </c>
     </row>
     <row r="17">
@@ -4653,10 +4791,10 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>1986217097.514784</v>
+        <v>1945662385.958666</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>6263060.504841177</v>
+        <v>6135180.922820581</v>
       </c>
     </row>
     <row r="23">
@@ -4678,7 +4816,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>9066267.680703618</v>
+        <v>8938388.098683022</v>
       </c>
     </row>
     <row r="25">
@@ -4688,7 +4826,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>19891.47439593931</v>
+        <v>21041.50083063317</v>
       </c>
     </row>
     <row r="26">
@@ -4698,7 +4836,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>9086159.155099558</v>
+        <v>8959429.599513656</v>
       </c>
     </row>
     <row r="28">
@@ -4725,7 +4863,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>9066267.680703618</v>
+        <v>8938388.098683022</v>
       </c>
     </row>
     <row r="32">
@@ -4735,7 +4873,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-2608266.10095845</v>
+        <v>-2736145.682979046</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -4865,7 +5003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5025,6 +5163,86 @@
       </c>
       <c r="J5" s="6" t="n">
         <v>19891.47439593931</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S61</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PYUSD in PYUSD/USDS Uniswap V4</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1030.276249266686</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1030.276249266686</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S62</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>USDT in USDT/USDS Uniswap V4</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>119.7501854271759</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>119.7501854271759</v>
       </c>
     </row>
   </sheetData>
@@ -5164,16 +5382,16 @@
         <v>110863143.4782853</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>88616292.08559048</v>
+        <v>91091279.19206849</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>73966626.05865648</v>
+        <v>74211501.64222991</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>275726915.1248708</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>3189409952.009573</v>
+        <v>3186690089.319521</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -5191,7 +5409,7 @@
         <v>0.03680583422201721</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>329157.4255864748</v>
+        <v>328871.5443734901</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>422088.5384580736</v>
@@ -5213,16 +5431,16 @@
         <v>110877925.9108401</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>86564422.08440566</v>
+        <v>91692006.16659966</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>71519833.45271687</v>
+        <v>71612483.73833267</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>295365472.0216876</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>3225279401.315834</v>
+        <v>3220059166.948024</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -5240,7 +5458,7 @@
         <v>0.03680583422201721</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>332927.6165281991</v>
+        <v>332378.924515697</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>427451.6176656627</v>
@@ -5262,16 +5480,16 @@
         <v>110877810.6471726</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>81952222.54390022</v>
+        <v>92077236.20493722</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>69759995.89224416</v>
+        <v>69854985.93062063</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>293845524.0721337</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>3224010853.102252</v>
+        <v>3213790849.402838</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -5289,7 +5507,7 @@
         <v>0.03680583422201721</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>332794.2810832317</v>
+        <v>331720.0698500753</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>426488.7538702118</v>
@@ -5311,16 +5529,16 @@
         <v>110892059.3807669</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>81400260.73180319</v>
+        <v>88843858.89968219</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>70641842.2466826</v>
+        <v>73417540.77615157</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>259701827.6324171</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>3170045015.962805</v>
+        <v>3159825719.265458</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -5338,7 +5556,7 @@
         <v>0.03680583422201721</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>327122.002465054</v>
+        <v>326047.8655439609</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>417263.8473377806</v>
@@ -5360,16 +5578,16 @@
         <v>110889172.1612514</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>69093022.25693116</v>
+        <v>69533991.50583017</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>31863872.09726685</v>
+        <v>41641283.76800805</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>207279980.22869</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>3106854058.297527</v>
+        <v>3096635677.377887</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -5387,7 +5605,7 @@
         <v>0.03680583422201721</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>320480.0834839636</v>
+        <v>319406.0428190686</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>399742.1334906419</v>
@@ -5409,16 +5627,16 @@
         <v>111007257.3918854</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>77569947.69440159</v>
+        <v>79253012.95639059</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>43308788.01971861</v>
+        <v>51845841.4035126</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>219866569.9365954</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>3112923574.767181</v>
+        <v>3102703456.121398</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -5436,7 +5654,7 @@
         <v>0.03680583422201721</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>321118.0424283331</v>
+        <v>320043.8191133141</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>403809.4229262104</v>
@@ -5458,16 +5676,16 @@
         <v>111027715.4453579</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>76788367.46748298</v>
+        <v>78076380.92033099</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>50808350.73815645</v>
+        <v>59740402.97761387</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>233820162.1960171</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>3136257482.403338</v>
+        <v>3126037416.711033</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -5485,7 +5703,7 @@
         <v>0.03680583422201721</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>323570.6389667894</v>
+        <v>322496.4212176412</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>408436.9319920092</v>
@@ -5507,16 +5725,16 @@
         <v>111120161.3432336</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>75760182.44680062</v>
+        <v>76977750.60328962</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>70007775.93805042</v>
+        <v>79010270.68734147</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>247432620.1013258</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>3076827279.99774</v>
+        <v>3066607217.091959</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -5534,7 +5752,7 @@
         <v>0.03680583422201721</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>317324.0080564197</v>
+        <v>316249.7906001595</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>405540.7609192973</v>
@@ -5556,16 +5774,16 @@
         <v>111173504.9761764</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>80050815.6017576</v>
+        <v>83986995.1391526</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>67941967.31765833</v>
+        <v>74224761.78704096</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>238697706.7029445</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>3058083368.048657</v>
+        <v>3047864394.041879</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -5583,7 +5801,7 @@
         <v>0.03680583422201721</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>315353.8599663408</v>
+        <v>314279.7569628318</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>402891.9527757948</v>
@@ -5605,16 +5823,16 @@
         <v>111194332.1398127</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>81275187.69112274</v>
+        <v>88285885.87971774</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>71623507.15292946</v>
+        <v>74834453.5301868</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>238206862.499659</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>3047896657.267934</v>
+        <v>3037675012.702082</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -5632,7 +5850,7 @@
         <v>0.03680583422201721</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>314283.1481083602</v>
+        <v>313208.7644058768</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>402287.4920322661</v>
@@ -5654,16 +5872,16 @@
         <v>111060579.317069</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>81215947.91151083</v>
+        <v>88325228.61914782</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>67845517.37781033</v>
+        <v>70954423.32702413</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>237780248.9173348</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>3041743187.662122</v>
+        <v>3031525001.005271</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -5681,7 +5899,7 @@
         <v>0.03680583422201721</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>313636.3649595607</v>
+        <v>312562.3447133736</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>401178.4833189916</v>
@@ -5703,16 +5921,16 @@
         <v>111188026.9078405</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>78997567.51920974</v>
+        <v>81940718.48437874</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>65237491.89061948</v>
+        <v>72514340.04445513</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>229796725.1160904</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3076479974.029222</v>
+        <v>3066259974.910218</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -5730,7 +5948,7 @@
         <v>0.03680583422201721</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>317287.5031799347</v>
+        <v>316213.2924282191</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>403496.5824205904</v>
@@ -5752,16 +5970,16 @@
         <v>111265821.539924</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>78765242.31002365</v>
+        <v>81225115.20416264</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>64786120.4074498</v>
+        <v>72546118.83705868</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>226868838.8186921</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>3019574693.956683</v>
+        <v>3009354822.632935</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -5779,7 +5997,7 @@
         <v>0.03680583422201721</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>311306.2635563777</v>
+        <v>310232.0662370546</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>397143.9109207783</v>
@@ -5801,16 +6019,16 @@
         <v>111094083.5824292</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>79471131.21310683</v>
+        <v>82726766.73606382</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>60666156.9094474</v>
+        <v>67630610.3862804</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>226543246.5083539</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>3029300410.635757</v>
+        <v>3019080321.635968</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -5828,7 +6046,7 @@
         <v>0.03680583422201721</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>312328.5209267696</v>
+        <v>311254.3007278022</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>397755.0456375423</v>
@@ -5850,16 +6068,16 @@
         <v>111092039.3505391</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>79482341.35048892</v>
+        <v>82885274.45428193</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>66641063.85555425</v>
+        <v>73458271.24311817</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>231469156.3066669</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>3039931130.746615</v>
+        <v>3029710990.255258</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -5877,7 +6095,7 @@
         <v>0.03688500088868387</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>313655.1101440299</v>
+        <v>312580.8845328511</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>400228.3688737685</v>
@@ -5899,16 +6117,16 @@
         <v>111194297.4469561</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>81248545.03625311</v>
+        <v>88174581.71420911</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>68286062.48687479</v>
+        <v>71580174.81251332</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>228136263.6824556</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>2767476272.26132</v>
+        <v>2757256123.257725</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -5926,7 +6144,7 @@
         <v>0.03688500088868387</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>285017.7360176659</v>
+        <v>283943.509511777</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>371609.9739917676</v>
@@ -5948,16 +6166,16 @@
         <v>111191712.9291975</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>80967462.51629348</v>
+        <v>87494168.87930548</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>79328906.40630278</v>
+        <v>83022107.32668166</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>229984484.7397425</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>2763048091.526166</v>
+        <v>2752828184.242775</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -5975,7 +6193,7 @@
         <v>0.03688500088868387</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>284552.2957274221</v>
+        <v>283478.0946284278</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>372469.6808233119</v>
@@ -5997,16 +6215,16 @@
         <v>111208330.4988015</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>81559483.04995982</v>
+        <v>90192905.40866883</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>71198474.75243124</v>
+        <v>72783894.76899749</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>229875387.3075938</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2738406665.089252</v>
+        <v>2728187822.713977</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6024,7 +6242,7 @@
         <v>0.03688500088868387</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>281962.2675965079</v>
+        <v>280888.178428614</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>369077.5797133897</v>
@@ -6046,16 +6264,16 @@
         <v>111239147.7397517</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>81156842.66544402</v>
+        <v>87813254.07817502</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>70973084.16176295</v>
+        <v>74536322.96352261</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>228544025.637105</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>2737102723.532863</v>
+        <v>2726883073.318372</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6073,7 +6291,7 @@
         <v>0.03688500088868387</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>281825.2120035306</v>
+        <v>280751.0379247125</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>368737.8140799199</v>
@@ -6095,16 +6313,16 @@
         <v>9329831.659127628</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>81822687.6721226</v>
+        <v>91452382.3922316</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>66255567.41316157</v>
+        <v>66846210.05367263</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>234890289.0773326</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>2855940846.675454</v>
+        <v>2845720509.314834</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6122,7 +6340,7 @@
         <v>0.03688500088868387</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>294316.1318272009</v>
+        <v>293241.8855233512</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>370758.3604021206</v>
@@ -6144,16 +6362,16 @@
         <v>9334369.363633053</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>81813150.25108935</v>
+        <v>91677504.76178636</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>65683498.36361798</v>
+        <v>66039713.46030262</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>234995824.5727294</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>2853174308.97369</v>
+        <v>2842953739.366308</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6171,7 +6389,7 @@
         <v>0.03688500088868387</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>294025.3446647309</v>
+        <v>292951.0739497275</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>370418.0109937783</v>
@@ -6193,16 +6411,16 @@
         <v>9332706.726220241</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>48597096.62418</v>
+        <v>57324084.49222599</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>74064594.53838435</v>
+        <v>75557150.62153183</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>244663090.2074062</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>2852720525.148238</v>
+        <v>2842500981.197045</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6220,7 +6438,7 @@
         <v>0.03688500088868387</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>293977.6480398508</v>
+        <v>292903.485130229</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>368775.8833457375</v>
@@ -6242,16 +6460,16 @@
         <v>9342149.173642222</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>48892875.67710059</v>
+        <v>58944069.04076159</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>71407736.84350848</v>
+        <v>71777177.29413517</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>240687318.9891957</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>2849463670.521194</v>
+        <v>2839043036.706906</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6269,7 +6487,7 @@
         <v>0.03688500088868387</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>293635.3243061197</v>
+        <v>292540.025103776</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>367768.4940876255</v>
@@ -6291,16 +6509,16 @@
         <v>9585296.355850186</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>12028752.84515581</v>
+        <v>86175124.32988481</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>32825711.63561737</v>
+        <v>51849352.42621429</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>238646466.469051</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>2900667521.503823</v>
+        <v>2807497509.228498</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6318,7 +6536,7 @@
         <v>0.03688500088868387</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>299017.2941687687</v>
+        <v>289224.3159347967</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>365031.4634654266</v>
@@ -6340,16 +6558,16 @@
         <v>9580019.549208868</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>12027024.55766915</v>
+        <v>120161291.8566851</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>2.726860306154629</v>
+        <v>41985005.35481693</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>269199092.0350934</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>2971702911.044312</v>
+        <v>2821583641.11734</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6367,7 +6585,7 @@
         <v>0.03688500088868387</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>306483.7311330145</v>
+        <v>290704.8908496163</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>372258.2433137374</v>
@@ -6389,16 +6607,16 @@
         <v>9601695.233795444</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>12033872.48206197</v>
+        <v>121838790.461726</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>2.878880678604907</v>
+        <v>40314178.52852874</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>277744609.8729502</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>2983991120.416507</v>
+        <v>2833872026.787195</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6416,7 +6634,7 @@
         <v>0.03688500088868387</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>307775.3287616677</v>
+        <v>291996.5070086862</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>374451.047250131</v>
@@ -6438,16 +6656,16 @@
         <v>9600955.315936545</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>12034552.12098754</v>
+        <v>122284572.4321135</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>3.370312549055434</v>
+        <v>39869042.06050103</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>275445094.1148835</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>2970474891.882532</v>
+        <v>2820355832.881217</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6465,7 +6683,7 @@
         <v>0.03688500088868387</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>306354.6556437179</v>
+        <v>290575.83753044</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>372788.6687517141</v>
@@ -6487,16 +6705,16 @@
         <v>9618262.413955124</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>12039742.08069779</v>
+        <v>121486092.0083568</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>3.312057178610368</v>
+        <v>40672778.77551679</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>275142578.7506528</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>2970478378.83077</v>
+        <v>2820359253.439651</v>
       </c>
       <c r="I33" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6514,7 +6732,7 @@
         <v>0.03688500088868387</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>306355.0221522904</v>
+        <v>290576.1970608669</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>372759.6028959002</v>
@@ -6536,16 +6754,16 @@
         <v>9618168.084080251</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>12038404.56699051</v>
+        <v>118967404.4272955</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>3.164221110747273</v>
+        <v>43189255.42830983</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>268307675.2718963</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>2956160844.299307</v>
+        <v>2806042592.174914</v>
       </c>
       <c r="I34" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6563,7 +6781,7 @@
         <v>0.03688500088868387</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>304850.124808106</v>
+        <v>289071.3915046069</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>370536.1472642949</v>
@@ -6585,16 +6803,16 @@
         <v>9619220.677902261</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>12032798.66154938</v>
+        <v>115633571.5610364</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>2.969736813081486</v>
+        <v>46519200.01361789</v>
       </c>
       <c r="G35" s="6" t="n">
         <v>268672569.1184176</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>2861087113.534848</v>
+        <v>2710967143.59148</v>
       </c>
       <c r="I35" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6612,7 +6830,7 @@
         <v>0.03688500088868387</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>294857.0492115556</v>
+        <v>279078.1353503489</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>371288.9686435931</v>
@@ -6637,7 +6855,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" s="12" t="n">
-        <v>9237350.035501989</v>
+        <v>9109470.453481393</v>
       </c>
       <c r="O37" s="12" t="n">
         <v>11674533.78166207</v>

--- a/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
+++ b/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -505,178 +505,188 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" s="4" t="n">
-        <v>11388147.15687342</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>+ distribution_rewards (settle-dr-dune)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1650764.59</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>13038911.74687342</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>8938388.098683022</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>8938388.098683022</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B11" s="3" t="n">
         <v>21041.50083063317</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" s="4" t="n">
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" s="4" t="n">
         <v>8959429.599513656</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>8938388.098683022</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>8938388.098683022</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B16" s="3" t="n">
         <v>-2736145.682979046</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" s="4" t="n">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" s="4" t="n">
         <v>11674533.78166207</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>sUSDS spread (Curve LP + PSM3) — deducted from sky_revenue</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B19" s="3" t="n">
         <v>171082.354798371</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>11273284.34691079</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>11273284.34691079</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B23" s="3" t="n">
         <v>-8938388.098683022</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" s="4" t="n">
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" s="4" t="n">
         <v>1353408.60867962</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-06-01 → 2026-06-30 (30 days)</t>
-        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>arbitrum=479089705, avalanche_c=89166730, base=48037326, ethereum=25433938, optimism=153632611, unichain=52115640</t>
+          <t>2026-06-01 → 2026-06-30 (30 days)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-07T01:10:59+00:00</t>
+          <t>arbitrum=479089705, avalanche_c=89166730, base=48037326, ethereum=25433938, optimism=153632611, unichain=52115640</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-07T14:51:29+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
+++ b/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>11273284.34691079</v>
+        <v>11273284.346911</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>13038911.74687342</v>
+        <v>13038911.74687362</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>11273284.34691079</v>
+        <v>11273284.346911</v>
       </c>
     </row>
     <row r="23">
@@ -641,7 +641,7 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1353408.60867962</v>
+        <v>1353408.608679825</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-07T14:51:29+00:00</t>
+          <t>2026-07-10T11:17:23+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3189433.596046247</v>
+        <v>3016814.373765289</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3189433.596046247</v>
+        <v>3016814.373765289</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-162760.0247831743</v>
+        <v>9859.197497783014</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -892,12 +892,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spark USDT (SparkLend spToken)</t>
+          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -907,44 +907,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>495837665.420656</v>
+        <v>608678684.51526</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>527947034.437084</v>
+        <v>206394227.300838</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>32109369.016428</v>
+        <v>-402284457.214422</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1098488.169145</v>
+        <v>0</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1098488.169145</v>
+        <v>0</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>496871361.4488988</v>
+        <v>595269202.6081126</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1187887.697872096</v>
+        <v>1346107.850553063</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1187887.697872096</v>
+        <v>1346107.850553063</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>-89399.52872709547</v>
+        <v>-1346107.850553063</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -957,12 +957,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Spark USDS (SparkLend spToken)</t>
+          <t>Spark USDT (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -976,62 +976,58 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>550178045.362034</v>
+        <v>495837665.420656</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>488789298.208332</v>
+        <v>527947034.437084</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-61388747.15370198</v>
+        <v>32109369.016428</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>996446.4198392286</v>
+        <v>1098488.169145</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>996446.4198392286</v>
+        <v>1098488.169145</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>391180692.315285</v>
+        <v>496871361.4488988</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>935209.3280067354</v>
+        <v>1123596.58022099</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>935209.3280067354</v>
+        <v>1123596.58022099</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>61237.09183249316</v>
+        <v>-25108.41107598991</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>156917846.5942976</v>
+        <v>0</v>
       </c>
       <c r="R4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>(avg excl. lending_idle)</t>
-        </is>
-      </c>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
+          <t>Spark USDS (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1041,52 +1037,56 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>608678684.51526</v>
+        <v>550178045.362034</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>206394227.300838</v>
+        <v>488789298.208332</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-402284457.214422</v>
+        <v>-61388747.15370198</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-5.37062273e-08</v>
+        <v>996446.4198392286</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-5.37062273e-08</v>
+        <v>996446.4198392286</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>382655180.7826357</v>
+        <v>391180692.315285</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>914827.0901611712</v>
+        <v>884593.7243238305</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>914827.0901611712</v>
+        <v>884593.7243238305</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-914827.0901612249</v>
+        <v>111852.6955153982</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>0</v>
+        <v>156917846.5942976</v>
       </c>
       <c r="R5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1137,13 +1137,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>612319.0022068904</v>
+        <v>579178.9393192878</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>612319.0022068904</v>
+        <v>579178.9393192878</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>952325.9977931136</v>
+        <v>985466.0606807162</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>423342.6581985646</v>
+        <v>400430.4143107537</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>423342.6581985646</v>
+        <v>400430.4143107537</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>90460.64578709904</v>
+        <v>113372.8896749099</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>89993374.27336854</v>
@@ -1271,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>343703.0723351669</v>
+        <v>325101.0995223077</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>308307.1858605666</v>
+        <v>289705.2130477073</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>73169.12215978043</v>
+        <v>91771.09497263966</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>330911.4404395117</v>
+        <v>313001.7791243019</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>296832.8862404924</v>
+        <v>278923.2249252826</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>60099.93650062312</v>
+        <v>78009.59781583288</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1401,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>300126.3403548375</v>
+        <v>283882.8369558939</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>269218.1561507764</v>
+        <v>252974.6527518328</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>49681.42864247441</v>
+        <v>65924.93204141797</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>251251.0702686146</v>
+        <v>237652.8049211904</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>251251.0702686146</v>
+        <v>237652.8049211904</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>163843.1129186988</v>
+        <v>177441.378266123</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>239072.8739760071</v>
+        <v>226133.71963043</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>239072.8739760071</v>
+        <v>226133.71963043</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-212305.5350290071</v>
+        <v>-199366.3806834299</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>231100.2638036835</v>
+        <v>218592.6048086293</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>231100.2638036835</v>
+        <v>218592.6048086293</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-200974.1192833513</v>
+        <v>-188466.4602882971</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1722,13 +1722,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>47069.39698180923</v>
+        <v>44521.89678920271</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>47069.39698180923</v>
+        <v>44521.89678920271</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>48577.92270840576</v>
+        <v>51125.42290101229</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>28690.77276117681</v>
+        <v>27137.96448612339</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>28690.77276117681</v>
+        <v>27137.96448612339</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>8663.573613823188</v>
+        <v>10216.38188887661</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>26721.36473021926</v>
+        <v>25275.145187121</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>26721.36473021926</v>
+        <v>25275.145187121</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>17424.72323703587</v>
+        <v>18870.94278013413</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1940,82 +1940,82 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>985396.9281006901</v>
+        <v>5019997.4</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>104354426.4993414</v>
+        <v>0</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>103369029.5712408</v>
+        <v>-5019997.4</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2857.341423254798</v>
+        <v>0</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>2857.341423254798</v>
+        <v>0</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>4430936.00242794</v>
+        <v>4852664.153333333</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>10593.19328043831</v>
+        <v>10973.53816437875</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>9502.264810668192</v>
+        <v>10973.53816437875</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-7735.851857183517</v>
+        <v>-10973.53816437875</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>1090.928469770123</v>
+        <v>0</v>
       </c>
       <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2024,13 +2024,13 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>4992819.462732</v>
+        <v>4997576.708614</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-4992819.462732</v>
+        <v>-4997576.708614</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>0</v>
@@ -2045,19 +2045,19 @@
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>3499154.7296384</v>
+        <v>4830990.818326866</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>8365.551285080261</v>
+        <v>10924.52731975241</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>8365.551285080261</v>
+        <v>10924.52731975241</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-8365.551285080261</v>
+        <v>-10924.52731975241</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2070,17 +2070,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2089,40 +2089,40 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>5019997.4</v>
+        <v>4992819.462732</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-5019997.4</v>
+        <v>-4992819.462732</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>6.056e-11</v>
+        <v>0</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>6.056e-11</v>
+        <v>0</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>3498646.8395605</v>
+        <v>4826392.1473076</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>8364.337054552565</v>
+        <v>10914.12814718641</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>8364.337054552565</v>
+        <v>10914.12814718641</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-8364.337054552505</v>
+        <v>-10914.12814718641</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2135,17 +2135,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2154,40 +2154,40 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>4997576.708614</v>
+        <v>4975417.167355</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-4997576.708614</v>
+        <v>-4975417.167355</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>1.4532344415e-08</v>
+        <v>0</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.4532344415e-08</v>
+        <v>0</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>3478277.793465591</v>
+        <v>4809569.928443166</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>8315.640065450647</v>
+        <v>10876.08734013992</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>8315.640065450647</v>
+        <v>10876.08734013992</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-8315.640065436115</v>
+        <v>-10876.08734013992</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2200,65 +2200,65 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>4975417.167355</v>
+        <v>985396.9281006901</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0</v>
+        <v>104354426.4993414</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-4975417.167355</v>
+        <v>103369029.5712408</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>5.95e-10</v>
+        <v>2857.341423254798</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>5.95e-10</v>
+        <v>2857.341423254798</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>3433368.776736433</v>
+        <v>4430936.00242794</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>8208.274512442043</v>
+        <v>10019.86615809035</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>8208.274512442043</v>
+        <v>8928.937688320224</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-8208.274512441449</v>
+        <v>-7162.52473483555</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>0</v>
+        <v>1090.928469770123</v>
       </c>
       <c r="S23" t="inlineStr"/>
     </row>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3490.101906688395</v>
+        <v>3301.209848374132</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3490.101906688395</v>
+        <v>3301.209848374132</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1421.014434796825</v>
+        <v>1609.906493111088</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2445,13 +2445,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>462.2034445262915</v>
+        <v>437.1879686660595</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>462.2034445262915</v>
+        <v>437.1879686660595</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>228.1344319024803</v>
+        <v>253.1499077627124</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2533,59 +2533,59 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>0</v>
+        <v>539.8728953809741</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0</v>
+        <v>637.4866706248019</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0</v>
+        <v>97.6137752438278</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>3.15299999999996e-10</v>
+        <v>97.6137752438278</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>3.15299999999996e-10</v>
+        <v>97.6137752438278</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>1206.634682533317</v>
+        <v>539.8728953809741</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>2.884743630680237</v>
+        <v>1.220837798409625</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>2.884743630680237</v>
+        <v>1.220837798409625</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-2.884743630364937</v>
+        <v>96.39293744541818</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2598,17 +2598,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2617,40 +2617,40 @@
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>539.8728953809741</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>637.4866706248019</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>97.6137752438278</v>
+        <v>0</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>97.6137752438278</v>
+        <v>0</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>97.6137752438278</v>
+        <v>0</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>539.8728953809741</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>1.290692965212494</v>
+        <v>0.6419890593344861</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1.290692965212494</v>
+        <v>0.6419890593344861</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>96.32308227861532</v>
+        <v>-0.6419890593344861</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2663,17 +2663,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2682,40 +2682,40 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>99.81305763596731</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>100.1238263246728</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0</v>
+        <v>0.3107686887055447</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0</v>
+        <v>0.3107686887055447</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0</v>
+        <v>0.3107686887055447</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>99.81305763596731</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.6787230569907252</v>
+        <v>0.2257115602198127</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.6787230569907252</v>
+        <v>0.2257115602198127</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-0.6787230569907252</v>
+        <v>0.08505712848573202</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2728,12 +2728,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2747,40 +2747,40 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>99.81305763596731</v>
+        <v>21.90661272343654</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>100.1238263246728</v>
+        <v>21.90842102645718</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.3107686887055447</v>
+        <v>0.001808303020639377</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.3107686887055447</v>
+        <v>0.0001839966329158897</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.3107686887055447</v>
+        <v>0.0001839966329158897</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>99.81305763596731</v>
+        <v>21.90693758471409</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.2386265590091936</v>
+        <v>0.04953910018384292</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2386265590091936</v>
+        <v>0.04953910018384292</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.07214212969635114</v>
+        <v>-0.04935510355092702</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2793,12 +2793,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2808,44 +2808,44 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>21.90661272343654</v>
+        <v>10.015998</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>21.90842102645718</v>
+        <v>1.353383</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.001808303020639377</v>
+        <v>-8.662615000000001</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.0001839966329158897</v>
+        <v>-8.662615000000001</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.0001839966329158897</v>
+        <v>-8.662615000000001</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>21.90693758471409</v>
+        <v>10.015998</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.05237367993810216</v>
+        <v>0.0226496070682828</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.05237367993810216</v>
+        <v>0.0226496070682828</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.05218968330518628</v>
+        <v>-8.685264607068282</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2858,12 +2858,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2873,44 +2873,44 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>10.015998</v>
+        <v>5.913258</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>1.353383</v>
+        <v>5.924825</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-8.662615000000001</v>
+        <v>0.011567</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-8.662615000000001</v>
+        <v>0.011567</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-8.662615000000001</v>
+        <v>0.011567</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>10.015998</v>
+        <v>5.913258</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.02394559584077611</v>
+        <v>0.01337190464628485</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.02394559584077611</v>
+        <v>0.01337190464628485</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-8.686560595840776</v>
+        <v>-0.001804904646284854</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2923,17 +2923,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2942,40 +2942,40 @@
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>5.913258</v>
+        <v>0.155165</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>5.924825</v>
+        <v>0.155607</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.011567</v>
+        <v>0.000442</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.011567</v>
+        <v>0.000442</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.011567</v>
+        <v>0.000442</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>5.913258</v>
+        <v>0.155165</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.01413703219292137</v>
+        <v>0.0003508812881901634</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.01413703219292137</v>
+        <v>0.0003508812881901634</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-0.002570032192921369</v>
+        <v>9.111871180983658e-05</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2988,17 +2988,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3007,40 +3007,40 @@
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>0.155165</v>
+        <v>0.057969</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.155607</v>
+        <v>0.058128</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.000442</v>
+        <v>0.000159</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.000442</v>
+        <v>0.000159</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.000442</v>
+        <v>0.000159</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.155165</v>
+        <v>0.057969</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.0003709583786492394</v>
+        <v>0.0001310877929629464</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.0003709583786492394</v>
+        <v>0.0001310877929629464</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>7.104162135076057e-05</v>
+        <v>2.791220703705357e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3053,17 +3053,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3072,40 +3072,40 @@
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.057969</v>
+        <v>0.006363</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.058128</v>
+        <v>0.006375</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.000159</v>
+        <v>1.2e-05</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.000159</v>
+        <v>1.2e-05</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.000159</v>
+        <v>1.2e-05</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.057969</v>
+        <v>0.006363</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.000138588510630089</v>
+        <v>1.43889255744144e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.000138588510630089</v>
+        <v>1.43889255744144e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>2.0411489369911e-05</v>
+        <v>-2.388925574414396e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3118,17 +3118,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3137,40 +3137,40 @@
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>0.006363</v>
+        <v>0.005746426914602806</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.006375</v>
+        <v>0.005747618663969358</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>1.2e-05</v>
+        <v>1.191749366552e-06</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>1.2e-05</v>
+        <v>1.191749366552e-06</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>1.2e-05</v>
+        <v>1.191749366552e-06</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.006363</v>
+        <v>0.005746426914602806</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.521224608220353e-05</v>
+        <v>1.299464233742441e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.521224608220353e-05</v>
+        <v>1.299464233742441e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-3.212246082203528e-06</v>
+        <v>-1.180289297087241e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3183,17 +3183,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3202,40 +3202,40 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.005746426914602806</v>
+        <v>0.001705</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.005747618663969358</v>
+        <v>0.001709</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>1.191749366552e-06</v>
+        <v>4e-06</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>1.191749366552e-06</v>
+        <v>4e-06</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>1.191749366552e-06</v>
+        <v>4e-06</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.005746426914602806</v>
+        <v>0.001705</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.373818329692526e-05</v>
+        <v>3.855589832528139e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.373818329692526e-05</v>
+        <v>3.855589832528139e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-1.254643393037326e-05</v>
+        <v>1.444101674718614e-07</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3248,59 +3248,59 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.001705</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.001709</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>4e-06</v>
+        <v>0</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>4e-06</v>
+        <v>0</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>4e-06</v>
+        <v>0</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.001705</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>4.076202981322807e-06</v>
+        <v>2.804392482394191e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>4.076202981322807e-06</v>
+        <v>2.804392482394191e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-7.620298132280616e-08</v>
+        <v>-2.804392482394191e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3313,12 +3313,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3328,44 +3328,44 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.000521673271312833</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.000522139801452544</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0</v>
+        <v>4.66530139711e-07</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0</v>
+        <v>4.6653013971e-07</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>0</v>
+        <v>4.6653013971e-07</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.000521673271312833</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>2.964857127979014e-06</v>
+        <v>1.179682205733403e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>2.964857127979014e-06</v>
+        <v>1.179682205733403e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-2.964857127979014e-06</v>
+        <v>-7.13152066023403e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3378,12 +3378,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3393,44 +3393,44 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0.000521673271312833</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.000522139801452544</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>4.66530139711e-07</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>4.6653013971e-07</v>
+        <v>0</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>4.6653013971e-07</v>
+        <v>0</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.000521673271312833</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.247182489033309e-06</v>
+        <v>1.693661699975317e-07</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.247182489033309e-06</v>
+        <v>1.693661699975317e-07</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-7.806523493233086e-07</v>
+        <v>-1.693661699975317e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3443,12 +3443,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Maple syrupUSDT (ERC-4626)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3458,14 +3458,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
@@ -3483,19 +3483,19 @@
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>1.790571396507918e-07</v>
+        <v>0</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1.790571396507918e-07</v>
+        <v>0</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-1.790571396507918e-07</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3508,12 +3508,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Maple syrupUSDT (ERC-4626)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
@@ -3573,12 +3573,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3638,12 +3638,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="M45" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" s="6" t="n">
         <v>0</v>
@@ -3698,17 +3698,21 @@
       <c r="R45" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3746,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" s="6" t="n">
         <v>0</v>
@@ -3763,21 +3767,17 @@
       <c r="R46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -3800,13 +3800,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0</v>
+        <v>1435964.694856968</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0</v>
+        <v>1435964.694856968</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0</v>
@@ -3824,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0</v>
+        <v>1435964.694856968</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -3837,12 +3837,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3865,13 +3865,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>1435964.694856968</v>
+        <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>1435964.694856968</v>
+        <v>0</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
@@ -3889,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>1435964.694856968</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="6" t="n">
         <v>0</v>
@@ -3902,12 +3902,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3930,13 +3930,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>7.364216e-08</v>
+        <v>0</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>7.364216e-08</v>
+        <v>0</v>
       </c>
       <c r="K49" s="6" t="n">
         <v>0</v>
@@ -3945,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>7.364216e-08</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="6" t="n">
         <v>0</v>
@@ -3962,22 +3962,26 @@
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3986,28 +3990,28 @@
         </is>
       </c>
       <c r="E50" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0</v>
+        <v>146550618.2104181</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0</v>
+        <v>81380618.21041812</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-2.3626413e-07</v>
+        <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-2.3626413e-07</v>
+        <v>0</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>1925.254906924896</v>
+        <v>67882687.2736806</v>
       </c>
       <c r="M50" s="7" t="n">
         <v>0</v>
@@ -4019,67 +4023,67 @@
         <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>-2.3626413e-07</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="6" t="n">
-        <v>0</v>
+        <v>67882687.2736806</v>
       </c>
       <c r="R50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+          <t>CoF excluded (already deducted from utilized)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>146550618.2104181</v>
+        <v>0</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>81380618.21041812</v>
+        <v>0</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>-2.524958539e-09</v>
+        <v>0</v>
       </c>
       <c r="I51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>-2.524958539e-09</v>
+        <v>0</v>
       </c>
       <c r="K51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>95010226.6771533</v>
+        <v>0</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>0</v>
@@ -4088,7 +4092,7 @@
         <v>0</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>-2.524958539e-09</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
         <v>0</v>
@@ -4096,21 +4100,17 @@
       <c r="R51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
-        </is>
-      </c>
+      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>USDS raw (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4120,14 +4120,14 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
@@ -4145,10 +4145,10 @@
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="M52" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N52" s="6" t="n">
         <v>0</v>
@@ -4160,27 +4160,31 @@
         <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr"/>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S48</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>USDS raw (Optimism — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4189,13 +4193,13 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>90000000</v>
+        <v>89900000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>90000000</v>
+        <v>100304256.5863323</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>0</v>
+        <v>10404256.58633234</v>
       </c>
       <c r="H53" s="6" t="n">
         <v>0</v>
@@ -4210,7 +4214,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>90000000</v>
+        <v>90246808.55287774</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4225,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>90000000</v>
+        <v>90246808.55287774</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
@@ -4239,17 +4243,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>USDS raw (Unichain — POL)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4261,25 +4265,25 @@
         <v>89900000</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>100304256.5863323</v>
+        <v>99990828.81481861</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>10404256.58633234</v>
+        <v>10090828.81481861</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-1.484488714e-09</v>
+        <v>0</v>
       </c>
       <c r="I54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-1.484488714e-09</v>
+        <v>0</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>93715560.74832186</v>
+        <v>90236360.96049395</v>
       </c>
       <c r="M54" s="7" t="n">
         <v>0</v>
@@ -4291,34 +4295,34 @@
         <v>0</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>-1.484488714e-09</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="6" t="n">
-        <v>0</v>
+        <v>90236360.96049395</v>
       </c>
       <c r="R54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+          <t>CoF excluded (already deducted from utilized)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4327,31 +4331,31 @@
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>99990828.81481861</v>
+        <v>0</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>10090828.81481861</v>
+        <v>0</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-2.98022377e-10</v>
+        <v>0</v>
       </c>
       <c r="I55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>-2.98022377e-10</v>
+        <v>0</v>
       </c>
       <c r="K55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>93600637.23210016</v>
+        <v>0</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" s="6" t="n">
         <v>0</v>
@@ -4360,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>-2.98022377e-10</v>
+        <v>0</v>
       </c>
       <c r="Q55" s="6" t="n">
         <v>0</v>
@@ -4368,11 +4372,7 @@
       <c r="R55" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
-        </is>
-      </c>
+      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">

--- a/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
+++ b/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>11273284.346911</v>
+        <v>11273284.346913</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>13038911.74687362</v>
+        <v>13038911.74687562</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>11273284.346911</v>
+        <v>11273284.346913</v>
       </c>
     </row>
     <row r="23">
@@ -641,7 +641,7 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1353408.608679825</v>
+        <v>1353408.608681825</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-10T11:17:23+00:00</t>
+          <t>2026-07-13T18:39:52+00:00</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
         <v>3016814.373765289</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>9859.197497783014</v>
+        <v>9859.197497782963</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -985,19 +985,19 @@
         <v>32109369.016428</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>1098488.169145</v>
+        <v>1098488.169146</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1098488.169145</v>
+        <v>1098488.169146</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>496871361.4488988</v>
+        <v>496871361.4488987</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>1</v>
@@ -1009,7 +1009,7 @@
         <v>1123596.58022099</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-25108.41107598991</v>
+        <v>-25108.41107498985</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1277,7 +1277,7 @@
         <v>289705.2130477073</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>91771.09497263966</v>
+        <v>91771.09497263965</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1401,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>283882.8369558939</v>
+        <v>283882.836955894</v>
       </c>
       <c r="O10" s="6" t="n">
         <v>252974.6527518328</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>65924.93204141797</v>
+        <v>65924.93204141795</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1769,31 +1769,31 @@
         <v>-5443040.8622</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>37354.346375</v>
+        <v>37354.346376</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>37354.346375</v>
+        <v>37354.346376</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>12000817.37390117</v>
+        <v>12000817.37390113</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>27137.96448612339</v>
+        <v>27137.96448612331</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>27137.96448612339</v>
+        <v>27137.96448612331</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>10216.38188887661</v>
+        <v>10216.38188987669</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -3341,13 +3341,13 @@
         <v>4.66530139711e-07</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>4.6653013971e-07</v>
+        <v>4.66530139711e-07</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>4.6653013971e-07</v>
+        <v>4.66530139711e-07</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
@@ -3365,7 +3365,7 @@
         <v>1.179682205733403e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-7.13152066023403e-07</v>
+        <v>-7.131520660224029e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>

--- a/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
+++ b/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>11273284.346913</v>
+        <v>11279641.55178227</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>13038911.74687562</v>
+        <v>13045268.95174489</v>
       </c>
     </row>
     <row r="9">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8938388.098683022</v>
+        <v>8938388.0890132</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>8959429.599513656</v>
+        <v>8959429.589843834</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>8938388.098683022</v>
+        <v>8938388.0890132</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-2736145.682979046</v>
+        <v>-2736145.692648868</v>
       </c>
     </row>
     <row r="17">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>171082.354798371</v>
+        <v>171082.3644681933</v>
       </c>
     </row>
     <row r="21">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>11273284.346913</v>
+        <v>11279641.55178227</v>
       </c>
     </row>
     <row r="23">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-8938388.098683022</v>
+        <v>-8938388.0890132</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1353408.608681825</v>
+        <v>1359765.813551093</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-13T18:39:52+00:00</t>
+          <t>2026-07-20T09:02:29+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3016814.373765289</v>
+        <v>3016814.344352271</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3016814.373765289</v>
+        <v>3016814.344352271</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>9859.197497782963</v>
+        <v>9859.226910800955</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1346107.850553063</v>
+        <v>1346107.837428922</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1346107.850553063</v>
+        <v>1346107.837428922</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>-1346107.850553063</v>
+        <v>-1346107.837428922</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1123596.58022099</v>
+        <v>1123596.569266267</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1123596.58022099</v>
+        <v>1123596.569266267</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-25108.41107498985</v>
+        <v>-25108.40012026665</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>884593.7243238305</v>
+        <v>884593.715699312</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>884593.7243238305</v>
+        <v>884593.715699312</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>111852.6955153982</v>
+        <v>111852.7041399166</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>156917846.5942976</v>
@@ -1137,13 +1137,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>579178.9393192878</v>
+        <v>579178.9336724702</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>579178.9393192878</v>
+        <v>579178.9336724702</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>985466.0606807162</v>
+        <v>985466.0663275338</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>400430.4143107537</v>
+        <v>400430.4104066796</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>400430.4143107537</v>
+        <v>400430.4104066796</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>113372.8896749099</v>
+        <v>113372.8935789841</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>89993374.27336854</v>
@@ -1247,19 +1247,19 @@
         <v>143764611.5800855</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>144181483.7745804</v>
+        <v>144183127.2756985</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>416872.1944949473</v>
+        <v>418515.6956130954</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>416872.1944949473</v>
+        <v>418515.6956130954</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>416872.1944949473</v>
+        <v>418515.6956130954</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>0</v>
@@ -1271,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>325101.0995223077</v>
+        <v>325101.0963526713</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>289705.2130477073</v>
+        <v>289705.209878071</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>91771.09497263965</v>
+        <v>93414.59926042407</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1312,19 +1312,19 @@
         <v>102351428.4607548</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>201093205.1965842</v>
+        <v>201095497.4250933</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>98741776.73582943</v>
+        <v>98744068.96433853</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>391011.3769401348</v>
+        <v>393303.6054492357</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>391011.3769401348</v>
+        <v>393303.6054492357</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>0</v>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>313001.7791243019</v>
+        <v>313001.7760726303</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>278923.2249252826</v>
+        <v>278923.221873611</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>78009.59781583288</v>
+        <v>80301.82937660547</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1377,19 +1377,19 @@
         <v>76003428.29531698</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>211443541.1594051</v>
+        <v>211445951.3696985</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>135440112.8640881</v>
+        <v>135442523.0743815</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>349807.7689973119</v>
+        <v>352217.9792907777</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>349807.7689973119</v>
+        <v>352217.9792907777</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0</v>
@@ -1401,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>283882.836955894</v>
+        <v>283882.8341881231</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>252974.6527518328</v>
+        <v>252974.6499840619</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>65924.93204141795</v>
+        <v>68335.14510265466</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>237652.8049211904</v>
+        <v>237652.8026041482</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>237652.8049211904</v>
+        <v>237652.8026041482</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>177441.378266123</v>
+        <v>177441.3805831652</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>226133.71963043</v>
+        <v>226133.7174256953</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>226133.71963043</v>
+        <v>226133.7174256953</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-199366.3806834299</v>
+        <v>-199366.3784786953</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>218592.6048086293</v>
+        <v>218592.6026774182</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>218592.6048086293</v>
+        <v>218592.6026774182</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-188466.4602882971</v>
+        <v>-188466.458157086</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1722,13 +1722,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>44521.89678920271</v>
+        <v>44521.89635512782</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>44521.89678920271</v>
+        <v>44521.89635512782</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>51125.42290101229</v>
+        <v>51125.42333508717</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>27137.96448612331</v>
+        <v>27137.96422153645</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>27137.96448612331</v>
+        <v>27137.96422153645</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>10216.38188987669</v>
+        <v>10216.38215446355</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>25275.145187121</v>
+        <v>25275.14494069606</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>25275.145187121</v>
+        <v>25275.14494069606</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>18870.94278013413</v>
+        <v>18870.94302655907</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>10973.53816437875</v>
+        <v>10973.53805739011</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>10973.53816437875</v>
+        <v>10973.53805739011</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-10973.53816437875</v>
+        <v>-10973.53805739011</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2051,13 +2051,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>10924.52731975241</v>
+        <v>10924.52721324161</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>10924.52731975241</v>
+        <v>10924.52721324161</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-10924.52731975241</v>
+        <v>-10924.52721324161</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2116,13 +2116,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>10914.12814718641</v>
+        <v>10914.128040777</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>10914.12814718641</v>
+        <v>10914.128040777</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-10914.12814718641</v>
+        <v>-10914.128040777</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2181,13 +2181,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>10876.08734013992</v>
+        <v>10876.08723410139</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>10876.08734013992</v>
+        <v>10876.08723410139</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-10876.08734013992</v>
+        <v>-10876.08723410139</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2222,43 +2222,43 @@
         <v>985396.9281006901</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>104354426.4993414</v>
+        <v>104355616.018357</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>103369029.5712408</v>
+        <v>103370219.0902563</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2857.341423254798</v>
+        <v>2868.606371807529</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>2857.341423254798</v>
+        <v>2868.606371807529</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>4430936.00242794</v>
+        <v>4430975.277563506</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>10019.86615809035</v>
+        <v>10019.95487495214</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>8928.937688320224</v>
+        <v>8929.016735359764</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-7162.52473483555</v>
+        <v>-7151.348503144608</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>1090.928469770123</v>
+        <v>1090.938139592373</v>
       </c>
       <c r="S23" t="inlineStr"/>
     </row>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3301.209848374132</v>
+        <v>3301.209816188345</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3301.209848374132</v>
+        <v>3301.209816188345</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1609.906493111088</v>
+        <v>1609.906525296875</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2445,13 +2445,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>437.1879686660595</v>
+        <v>437.1879644036105</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>437.1879686660595</v>
+        <v>437.1879644036105</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>253.1499077627124</v>
+        <v>253.1499120251614</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2579,13 +2579,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>1.220837798409625</v>
+        <v>1.22083778650683</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.220837798409625</v>
+        <v>1.22083778650683</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>96.39293744541818</v>
+        <v>96.39293745732098</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2644,13 +2644,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.6419890593344861</v>
+        <v>0.6419890530752891</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.6419890593344861</v>
+        <v>0.6419890530752891</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.6419890593344861</v>
+        <v>-0.6419890530752891</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2709,13 +2709,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2257115602198127</v>
+        <v>0.225711558019194</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2257115602198127</v>
+        <v>0.225711558019194</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08505712848573202</v>
+        <v>0.08505713068635073</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2774,13 +2774,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.04953910018384292</v>
+        <v>0.04953909970085183</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.04953910018384292</v>
+        <v>0.04953909970085183</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.04935510355092702</v>
+        <v>-0.04935510306793594</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2839,13 +2839,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.0226496070682828</v>
+        <v>0.02264960684745605</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.0226496070682828</v>
+        <v>0.02264960684745605</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-8.685264607068282</v>
+        <v>-8.685264606847456</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.01337190464628485</v>
+        <v>0.01337190451591287</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.01337190464628485</v>
+        <v>0.01337190451591287</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.001804904646284854</v>
+        <v>-0.001804904515912871</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2969,13 +2969,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.0003508812881901634</v>
+        <v>0.0003508812847691781</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.0003508812881901634</v>
+        <v>0.0003508812847691781</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>9.111871180983658e-05</v>
+        <v>9.111871523082189e-05</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3034,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.0001310877929629464</v>
+        <v>0.0001310877916848805</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.0001310877929629464</v>
+        <v>0.0001310877916848805</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>2.791220703705357e-05</v>
+        <v>2.791220831511948e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3099,13 +3099,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.43889255744144e-05</v>
+        <v>1.438892543412677e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.43889255744144e-05</v>
+        <v>1.438892543412677e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-2.388925574414396e-06</v>
+        <v>-2.388925434126771e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.299464233742441e-05</v>
+        <v>1.299464221073062e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.299464233742441e-05</v>
+        <v>1.299464221073062e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.180289297087241e-05</v>
+        <v>-1.180289284417862e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>3.855589832528139e-06</v>
+        <v>3.855589794937317e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>3.855589832528139e-06</v>
+        <v>3.855589794937317e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.444101674718614e-07</v>
+        <v>1.444102050626837e-07</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>2.804392482394191e-06</v>
+        <v>2.804392455052222e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>2.804392482394191e-06</v>
+        <v>2.804392455052222e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-2.804392482394191e-06</v>
+        <v>-2.804392455052222e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.179682205733403e-06</v>
+        <v>1.179682194231862e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.179682205733403e-06</v>
+        <v>1.179682194231862e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-7.131520660224029e-07</v>
+        <v>-7.13152054520862e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.693661699975317e-07</v>
+        <v>1.693661683462633e-07</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.693661699975317e-07</v>
+        <v>1.693661683462633e-07</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.693661699975317e-07</v>
+        <v>-1.693661683462633e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>8938388.098683022</v>
+        <v>8938388.0890132</v>
       </c>
     </row>
     <row r="25">
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>8959429.599513656</v>
+        <v>8959429.589843834</v>
       </c>
     </row>
     <row r="28">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>8938388.098683022</v>
+        <v>8938388.0890132</v>
       </c>
     </row>
     <row r="32">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-2736145.682979046</v>
+        <v>-2736145.692648868</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>171082.354798371</v>
+        <v>171082.3644681933</v>
       </c>
     </row>
     <row r="37">

--- a/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
+++ b/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8938388.0890132</v>
+        <v>9053787.675606435</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>8959429.589843834</v>
+        <v>9074829.176437067</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>8938388.0890132</v>
+        <v>9053787.675606435</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
-        <v>11674533.78166207</v>
+        <v>11789933.3682553</v>
       </c>
     </row>
     <row r="19">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-8938388.0890132</v>
+        <v>-9053787.675606435</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1359765.813551093</v>
+        <v>1244366.226957858</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-20T09:02:29+00:00</t>
+          <t>2026-07-30T23:27:03+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3016814.344352271</v>
+        <v>3055031.618335935</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3016814.344352271</v>
+        <v>3055031.618335935</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>9859.226910800955</v>
+        <v>-28358.04707286318</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1346107.837428922</v>
+        <v>1363160.451929674</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1346107.837428922</v>
+        <v>1363160.451929674</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>-1346107.837428922</v>
+        <v>-1363160.451929674</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1123596.569266267</v>
+        <v>1137830.391117168</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1123596.569266267</v>
+        <v>1137830.391117168</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-25108.40012026665</v>
+        <v>-39342.22197116799</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>884593.715699312</v>
+        <v>895799.8280212046</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>884593.715699312</v>
+        <v>895799.8280212046</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>111852.7041399166</v>
+        <v>100646.591818024</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>156917846.5942976</v>
@@ -1137,13 +1137,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>579178.9336724702</v>
+        <v>586516.0242147387</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>579178.9336724702</v>
+        <v>586516.0242147387</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>985466.0663275338</v>
+        <v>978128.9757852652</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>400430.4104066796</v>
+        <v>405503.0986662512</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>400430.4104066796</v>
+        <v>405503.0986662512</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>113372.8935789841</v>
+        <v>108300.2053194124</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>89993374.27336854</v>
@@ -1271,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>325101.0963526713</v>
+        <v>329219.5061232159</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>289705.209878071</v>
+        <v>293823.6196486157</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>93414.59926042407</v>
+        <v>89296.18948987943</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>313001.7760726303</v>
+        <v>316966.9105715215</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>278923.221873611</v>
+        <v>282888.3563725022</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>80301.82937660547</v>
+        <v>76336.69487771421</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1401,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>283882.8341881231</v>
+        <v>287479.0873263837</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>252974.6499840619</v>
+        <v>256570.9031223226</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>68335.14510265466</v>
+        <v>64738.89196439401</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>237652.8026041482</v>
+        <v>240663.4095667912</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>237652.8026041482</v>
+        <v>240663.4095667912</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>177441.3805831652</v>
+        <v>174430.7736205222</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>226133.7174256953</v>
+        <v>228998.3995868569</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>226133.7174256953</v>
+        <v>228998.3995868569</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-199366.3784786953</v>
+        <v>-202231.0606398569</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>218592.6026774182</v>
+        <v>221361.7533223575</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>218592.6026774182</v>
+        <v>221361.7533223575</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-188466.458157086</v>
+        <v>-191235.6088020253</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1722,13 +1722,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>44521.89635512782</v>
+        <v>45085.90372086498</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>44521.89635512782</v>
+        <v>45085.90372086498</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>51125.42333508717</v>
+        <v>50561.41596935</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>27137.96422153645</v>
+        <v>27481.75037992401</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>27137.96422153645</v>
+        <v>27481.75037992401</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>10216.38215446355</v>
+        <v>9872.595996075994</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>25275.14494069606</v>
+        <v>25595.33273779525</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>25275.14494069606</v>
+        <v>25595.33273779525</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>18870.94302655907</v>
+        <v>18550.75522945988</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>10973.53805739011</v>
+        <v>11112.55181914</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>10973.53805739011</v>
+        <v>11112.55181914</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-10973.53805739011</v>
+        <v>-11112.55181914</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2051,13 +2051,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>10924.52721324161</v>
+        <v>11062.92010123356</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>10924.52721324161</v>
+        <v>11062.92010123356</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-10924.52721324161</v>
+        <v>-11062.92010123356</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2116,13 +2116,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>10914.128040777</v>
+        <v>11052.38919112191</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>10914.128040777</v>
+        <v>11052.38919112191</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-10914.128040777</v>
+        <v>-11052.38919112191</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2181,13 +2181,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>10876.08723410139</v>
+        <v>11013.86648010439</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>10876.08723410139</v>
+        <v>11013.86648010439</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-10876.08723410139</v>
+        <v>-11013.86648010439</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2246,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>10019.95487495214</v>
+        <v>10146.88855964403</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>8929.016735359764</v>
+        <v>9055.95042005166</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-7151.348503144608</v>
+        <v>-7278.282187836503</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3301.209816188345</v>
+        <v>3343.029837449852</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3301.209816188345</v>
+        <v>3343.029837449852</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1609.906525296875</v>
+        <v>1568.086504035368</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2445,13 +2445,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>437.1879644036105</v>
+        <v>442.7263006453657</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>437.1879644036105</v>
+        <v>442.7263006453657</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>253.1499120251614</v>
+        <v>247.6115757834062</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2579,13 +2579,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>1.22083778650683</v>
+        <v>1.236303468796457</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.22083778650683</v>
+        <v>1.236303468796457</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>96.39293745732098</v>
+        <v>96.37747177503135</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2644,13 +2644,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.6419890530752891</v>
+        <v>0.6501218278288377</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.6419890530752891</v>
+        <v>0.6501218278288377</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.6419890530752891</v>
+        <v>-0.6501218278288377</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2709,13 +2709,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.225711558019194</v>
+        <v>0.2285708922272297</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.225711558019194</v>
+        <v>0.2285708922272297</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08505713068635073</v>
+        <v>0.08219779647831503</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2774,13 +2774,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.04953909970085183</v>
+        <v>0.05016666544738702</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.04953909970085183</v>
+        <v>0.05016666544738702</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.04935510306793594</v>
+        <v>-0.04998266881447113</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2839,13 +2839,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.02264960684745605</v>
+        <v>0.02293653409312233</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.02264960684745605</v>
+        <v>0.02293653409312233</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-8.685264606847456</v>
+        <v>-8.685551534093122</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.01337190451591287</v>
+        <v>0.01354130099850543</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.01337190451591287</v>
+        <v>0.01354130099850543</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.001804904515912871</v>
+        <v>-0.001974300998505425</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2969,13 +2969,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.0003508812847691781</v>
+        <v>0.0003553262802727522</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.0003508812847691781</v>
+        <v>0.0003553262802727522</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>9.111871523082189e-05</v>
+        <v>8.667371972724776e-05</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3034,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.0001310877916848805</v>
+        <v>0.0001327484235564153</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.0001310877916848805</v>
+        <v>0.0001327484235564153</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>2.791220831511948e-05</v>
+        <v>2.625157644358474e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3099,13 +3099,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.438892543412677e-05</v>
+        <v>1.457120562868896e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.438892543412677e-05</v>
+        <v>1.457120562868896e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-2.388925434126771e-06</v>
+        <v>-2.57120562868896e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.299464221073062e-05</v>
+        <v>1.315925950069309e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.299464221073062e-05</v>
+        <v>1.315925950069309e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.180289284417862e-05</v>
+        <v>-1.196751013414109e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>3.855589794937317e-06</v>
+        <v>3.904432751361728e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>3.855589794937317e-06</v>
+        <v>3.904432751361728e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.444102050626837e-07</v>
+        <v>9.556724863827176e-08</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>2.804392455052222e-06</v>
+        <v>2.839918749540013e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>2.804392455052222e-06</v>
+        <v>2.839918749540013e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-2.804392455052222e-06</v>
+        <v>-2.839918749540013e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.179682194231862e-06</v>
+        <v>1.194626513796972e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.179682194231862e-06</v>
+        <v>1.194626513796972e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-7.13152054520862e-07</v>
+        <v>-7.280963740859724e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.693661683462633e-07</v>
+        <v>1.715117141175402e-07</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.693661683462633e-07</v>
+        <v>1.715117141175402e-07</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.693661683462633e-07</v>
+        <v>-1.715117141175402e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -4687,11 +4687,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reference rate (effr), period avg</t>
+          <t>Reference rate (tbill_3m), period avg</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.03625333333333333</v>
+        <v>0.03809333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.03684805644423943</v>
+        <v>0.0383047231109061</v>
       </c>
     </row>
     <row r="11">
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.03834079216689766</v>
+        <v>0.03883530459765357</v>
       </c>
     </row>
     <row r="12">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-7.67212098784927</v>
+        <v>-2.726996680290183</v>
       </c>
     </row>
     <row r="13">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>178971.2647868314</v>
+        <v>63571.67819359694</v>
       </c>
     </row>
     <row r="15">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9109470.453481393</v>
+        <v>9224870.040074628</v>
       </c>
     </row>
     <row r="17">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>178971.2647868314</v>
+        <v>63571.67819359694</v>
       </c>
     </row>
     <row r="19">
@@ -4791,7 +4791,7 @@
         <v>1000000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2974289.530660812</v>
+        <v>3089689.117254046</v>
       </c>
     </row>
     <row r="21">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>8938388.0890132</v>
+        <v>9053787.675606435</v>
       </c>
     </row>
     <row r="25">
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>8959429.589843834</v>
+        <v>9074829.176437067</v>
       </c>
     </row>
     <row r="28">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>11674533.78166207</v>
+        <v>11789933.3682553</v>
       </c>
     </row>
     <row r="31">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>8938388.0890132</v>
+        <v>9053787.675606435</v>
       </c>
     </row>
     <row r="32">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>effr</t>
+          <t>tbill_3m</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         <v>5</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>328871.5443734901</v>
+        <v>332216.9641822214</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>422088.5384580736</v>
+        <v>425433.9582668049</v>
       </c>
     </row>
     <row r="7">
@@ -5462,16 +5462,16 @@
         <v>5</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>332378.924515697</v>
+        <v>335724.3443244282</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>427451.6176656627</v>
+        <v>430797.037474394</v>
       </c>
     </row>
     <row r="8">
@@ -5511,16 +5511,16 @@
         <v>5</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>331720.0698500753</v>
+        <v>335065.4896588066</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>426488.7538702118</v>
+        <v>429834.173678943</v>
       </c>
     </row>
     <row r="9">
@@ -5560,16 +5560,16 @@
         <v>5</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>326047.8655439609</v>
+        <v>329393.2853526921</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>417263.8473377806</v>
+        <v>420609.2671465119</v>
       </c>
     </row>
     <row r="10">
@@ -5609,16 +5609,16 @@
         <v>5</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>319406.0428190686</v>
+        <v>322751.4626277998</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>399742.1334906419</v>
+        <v>403087.5532993731</v>
       </c>
     </row>
     <row r="11">
@@ -5658,16 +5658,16 @@
         <v>5</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>320043.8191133141</v>
+        <v>323389.2389220453</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>403809.4229262104</v>
+        <v>407154.8427349417</v>
       </c>
     </row>
     <row r="12">
@@ -5707,16 +5707,16 @@
         <v>5</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>322496.4212176412</v>
+        <v>325841.8410263725</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>408436.9319920092</v>
+        <v>411782.3518007405</v>
       </c>
     </row>
     <row r="13">
@@ -5756,16 +5756,16 @@
         <v>5</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.038</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03823083422201721</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>316249.7906001595</v>
+        <v>320013.1016180831</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>405540.7609192973</v>
+        <v>409304.0719372209</v>
       </c>
     </row>
     <row r="14">
@@ -5805,16 +5805,16 @@
         <v>5</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.038</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03823083422201721</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>314279.7569628318</v>
+        <v>318043.0679807554</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>402891.9527757948</v>
+        <v>406655.2637937185</v>
       </c>
     </row>
     <row r="15">
@@ -5854,16 +5854,16 @@
         <v>5</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.038</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03823083422201721</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>313208.7644058768</v>
+        <v>316972.0754238004</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>402287.4920322661</v>
+        <v>406050.8030501897</v>
       </c>
     </row>
     <row r="16">
@@ -5903,16 +5903,16 @@
         <v>5</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.038</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03823083422201721</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>312562.3447133736</v>
+        <v>316325.6557312972</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>401178.4833189916</v>
+        <v>404941.7943369151</v>
       </c>
     </row>
     <row r="17">
@@ -5952,16 +5952,16 @@
         <v>5</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.038</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03823083422201721</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>316213.2924282191</v>
+        <v>319976.6034461427</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>403496.5824205904</v>
+        <v>407259.893438514</v>
       </c>
     </row>
     <row r="18">
@@ -6001,16 +6001,16 @@
         <v>5</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.038</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03823083422201721</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>310232.0662370546</v>
+        <v>313995.3772549782</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>397143.9109207783</v>
+        <v>400907.221938702</v>
       </c>
     </row>
     <row r="19">
@@ -6050,16 +6050,16 @@
         <v>5</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.038</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03823083422201721</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>311254.3007278022</v>
+        <v>315017.6117457258</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>397755.0456375423</v>
+        <v>401518.3566554659</v>
       </c>
     </row>
     <row r="20">
@@ -6099,16 +6099,16 @@
         <v>5</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0379</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03815166755535054</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>312580.8845328511</v>
+        <v>315926.0497723278</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>400228.3688737685</v>
+        <v>403573.5341132453</v>
       </c>
     </row>
     <row r="21">
@@ -6148,16 +6148,16 @@
         <v>5</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0379</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03815166755535054</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>283943.509511777</v>
+        <v>287288.6747512537</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>371609.9739917676</v>
+        <v>374955.1392312443</v>
       </c>
     </row>
     <row r="22">
@@ -6197,16 +6197,16 @@
         <v>5</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0379</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03815166755535054</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>283478.0946284278</v>
+        <v>286823.2598679045</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>372469.6808233119</v>
+        <v>375814.8460627886</v>
       </c>
     </row>
     <row r="23">
@@ -6246,16 +6246,16 @@
         <v>5</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0379</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03815166755535054</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>280888.178428614</v>
+        <v>284233.3436680907</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>369077.5797133897</v>
+        <v>372422.7449528664</v>
       </c>
     </row>
     <row r="24">
@@ -6295,16 +6295,16 @@
         <v>5</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0379</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03815166755535054</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>280751.0379247125</v>
+        <v>284096.2031641892</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>368737.8140799199</v>
+        <v>372082.9793193966</v>
       </c>
     </row>
     <row r="25">
@@ -6344,16 +6344,16 @@
         <v>5</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0379</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03815166755535054</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>293241.8855233512</v>
+        <v>296587.0507628279</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>370758.3604021206</v>
+        <v>374103.5256415973</v>
       </c>
     </row>
     <row r="26">
@@ -6393,16 +6393,16 @@
         <v>5</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0379</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03815166755535054</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>292951.0739497275</v>
+        <v>296296.2391892042</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>370418.0109937783</v>
+        <v>373763.176233255</v>
       </c>
     </row>
     <row r="27">
@@ -6442,16 +6442,16 @@
         <v>5</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0385</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03862666755535054</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>292903.485130229</v>
+        <v>297502.0380628955</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>368775.8833457375</v>
+        <v>373374.436278404</v>
       </c>
     </row>
     <row r="28">
@@ -6491,16 +6491,16 @@
         <v>5</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0385</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03862666755535054</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>292540.025103776</v>
+        <v>297138.5780364425</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>367768.4940876255</v>
+        <v>372367.0470202919</v>
       </c>
     </row>
     <row r="29">
@@ -6540,16 +6540,16 @@
         <v>5</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0385</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03862666755535054</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>289224.3159347967</v>
+        <v>293822.8688674631</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>365031.4634654266</v>
+        <v>369630.016398093</v>
       </c>
     </row>
     <row r="30">
@@ -6589,16 +6589,16 @@
         <v>5</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0385</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03862666755535054</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>290704.8908496163</v>
+        <v>295303.4437822828</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>372258.2433137374</v>
+        <v>376856.7962464038</v>
       </c>
     </row>
     <row r="31">
@@ -6638,16 +6638,16 @@
         <v>5</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0385</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03862666755535054</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>291996.5070086862</v>
+        <v>296595.0599413526</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>374451.047250131</v>
+        <v>379049.6001827974</v>
       </c>
     </row>
     <row r="32">
@@ -6687,16 +6687,16 @@
         <v>5</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0385</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03862666755535054</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>290575.83753044</v>
+        <v>295174.3904631064</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>372788.6687517141</v>
+        <v>377387.2216843806</v>
       </c>
     </row>
     <row r="33">
@@ -6736,16 +6736,16 @@
         <v>5</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0385</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03862666755535054</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>290576.1970608669</v>
+        <v>295174.7499935334</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>372759.6028959002</v>
+        <v>377358.1558285666</v>
       </c>
     </row>
     <row r="34">
@@ -6785,16 +6785,16 @@
         <v>5</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0387</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03878500088868388</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>289071.3915046069</v>
+        <v>294087.6133054312</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>370536.1472642949</v>
+        <v>375552.3690651191</v>
       </c>
     </row>
     <row r="35">
@@ -6834,16 +6834,16 @@
         <v>5</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0387</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03878500088868388</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>279078.1353503489</v>
+        <v>284094.3571511732</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>371288.9686435931</v>
+        <v>376305.1904444174</v>
       </c>
     </row>
     <row r="37">
@@ -6865,10 +6865,10 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" s="12" t="n">
-        <v>9109470.453481393</v>
+        <v>9224870.040074628</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>11674533.78166207</v>
+        <v>11789933.3682553</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
+++ b/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9053787.675606435</v>
+        <v>9054205.487267924</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>9074829.176437067</v>
+        <v>9075246.988098558</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9053787.675606435</v>
+        <v>9054205.487267924</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
-        <v>11789933.3682553</v>
+        <v>11790351.17991679</v>
       </c>
     </row>
     <row r="19">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-9053787.675606435</v>
+        <v>-9054205.487267924</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1244366.226957858</v>
+        <v>1243948.415296367</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-30T23:27:03+00:00</t>
+          <t>2026-07-31T00:23:57+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3055031.618335935</v>
+        <v>3055169.986446361</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3055031.618335935</v>
+        <v>3055169.986446361</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-28358.04707286318</v>
+        <v>-28496.41518328837</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1363160.451929674</v>
+        <v>1363222.192022578</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1363160.451929674</v>
+        <v>1363222.192022578</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>-1363160.451929674</v>
+        <v>-1363222.192022578</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1137830.391117168</v>
+        <v>1137881.925589106</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1137830.391117168</v>
+        <v>1137881.925589106</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-39342.22197116799</v>
+        <v>-39393.75644310547</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>895799.8280212046</v>
+        <v>895840.4004751126</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>895799.8280212046</v>
+        <v>895840.4004751126</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>100646.591818024</v>
+        <v>100606.019364116</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>156917846.5942976</v>
@@ -1137,13 +1137,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>586516.0242147387</v>
+        <v>586542.5886252404</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>586516.0242147387</v>
+        <v>586542.5886252404</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>978128.9757852652</v>
+        <v>978102.4113747637</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>405503.0986662512</v>
+        <v>405521.4646619409</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>405503.0986662512</v>
+        <v>405521.4646619409</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>108300.2053194124</v>
+        <v>108281.8393237228</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>89993374.27336854</v>
@@ -1271,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>329219.5061232159</v>
+        <v>329234.4170919614</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>293823.6196486157</v>
+        <v>293838.5306173611</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>89296.18948987943</v>
+        <v>89281.27852113397</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>316966.9105715215</v>
+        <v>316981.2665972398</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>282888.3563725022</v>
+        <v>282902.7123982206</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>76336.69487771421</v>
+        <v>76322.3388519959</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1401,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>287479.0873263837</v>
+        <v>287492.1077932952</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>256570.9031223226</v>
+        <v>256583.9235892341</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>64738.89196439401</v>
+        <v>64725.87149748252</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>240663.4095667912</v>
+        <v>240674.3096638738</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>240663.4095667912</v>
+        <v>240674.3096638738</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>174430.7736205222</v>
+        <v>174419.8735234396</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>228998.3995868569</v>
+        <v>229008.7713537646</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>228998.3995868569</v>
+        <v>229008.7713537646</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-202231.0606398569</v>
+        <v>-202241.4324067646</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>221361.7533223575</v>
+        <v>221371.7792112366</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>221361.7533223575</v>
+        <v>221371.7792112366</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-191235.6088020253</v>
+        <v>-191245.6346909044</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1722,13 +1722,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>45085.90372086498</v>
+        <v>45087.94574598421</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>45085.90372086498</v>
+        <v>45087.94574598421</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>50561.41596935</v>
+        <v>50559.37394423078</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>27481.75037992401</v>
+        <v>27482.99507992921</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>27481.75037992401</v>
+        <v>27482.99507992921</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>9872.595996075994</v>
+        <v>9871.351296070787</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>25595.33273779525</v>
+        <v>25596.49199840826</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>25595.33273779525</v>
+        <v>25596.49199840826</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>18550.75522945988</v>
+        <v>18549.59596884687</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>11112.55181914</v>
+        <v>11113.05512744882</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>11112.55181914</v>
+        <v>11113.05512744882</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-11112.55181914</v>
+        <v>-11113.05512744882</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2051,13 +2051,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>11062.92010123356</v>
+        <v>11063.42116162881</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>11062.92010123356</v>
+        <v>11063.42116162881</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-11062.92010123356</v>
+        <v>-11063.42116162881</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2116,13 +2116,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11052.38919112191</v>
+        <v>11052.8897745525</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11052.38919112191</v>
+        <v>11052.8897745525</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11052.38919112191</v>
+        <v>-11052.8897745525</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2181,13 +2181,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11013.86648010439</v>
+        <v>11014.36531876916</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11013.86648010439</v>
+        <v>11014.36531876916</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11013.86648010439</v>
+        <v>-11014.36531876916</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2246,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>10146.88855964403</v>
+        <v>10147.34813125313</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>9055.95042005166</v>
+        <v>9056.409991660761</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-7278.282187836503</v>
+        <v>-7278.741759445605</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3343.029837449852</v>
+        <v>3343.181249539641</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3343.029837449852</v>
+        <v>3343.181249539641</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1568.086504035368</v>
+        <v>1567.935091945579</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2445,13 +2445,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>442.7263006453657</v>
+        <v>442.7463525496694</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>442.7263006453657</v>
+        <v>442.7463525496694</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>247.6115757834062</v>
+        <v>247.5915238791025</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2579,13 +2579,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>1.236303468796457</v>
+        <v>1.236359463298728</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.236303468796457</v>
+        <v>1.236359463298728</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>96.37747177503135</v>
+        <v>96.37741578052908</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2644,13 +2644,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.6501218278288377</v>
+        <v>0.650151273065451</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.6501218278288377</v>
+        <v>0.650151273065451</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.6501218278288377</v>
+        <v>-0.650151273065451</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2709,13 +2709,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2285708922272297</v>
+        <v>0.2285812446315275</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2285708922272297</v>
+        <v>0.2285812446315275</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08219779647831503</v>
+        <v>0.08218744407401721</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2774,13 +2774,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.05016666544738702</v>
+        <v>0.05016893758973168</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.05016666544738702</v>
+        <v>0.05016893758973168</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.04998266881447113</v>
+        <v>-0.04998494095681579</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2839,13 +2839,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.02293653409312233</v>
+        <v>0.02293757293175926</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.02293653409312233</v>
+        <v>0.02293757293175926</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-8.685551534093122</v>
+        <v>-8.685552572931758</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.01354130099850543</v>
+        <v>0.01354191430941868</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.01354130099850543</v>
+        <v>0.01354191430941868</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.001974300998505425</v>
+        <v>-0.001974914309418679</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2969,13 +2969,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.0003553262802727522</v>
+        <v>0.0003553423736662512</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.0003553262802727522</v>
+        <v>0.0003553423736662512</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>8.667371972724776e-05</v>
+        <v>8.665762633374878e-05</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3034,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.0001327484235564153</v>
+        <v>0.0001327544359814321</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.0001327484235564153</v>
+        <v>0.0001327544359814321</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>2.625157644358474e-05</v>
+        <v>2.624556401856786e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3099,13 +3099,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.457120562868896e-05</v>
+        <v>1.457186558591407e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.457120562868896e-05</v>
+        <v>1.457186558591407e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-2.57120562868896e-06</v>
+        <v>-2.57186558591407e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.315925950069309e-05</v>
+        <v>1.315985550823055e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.315925950069309e-05</v>
+        <v>1.315985550823055e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.196751013414109e-05</v>
+        <v>-1.196810614167855e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>3.904432751361728e-06</v>
+        <v>3.904609590442164e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>3.904432751361728e-06</v>
+        <v>3.904609590442164e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>9.556724863827176e-08</v>
+        <v>9.539040955783619e-08</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>2.839918749540013e-06</v>
+        <v>2.840047374785256e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>2.839918749540013e-06</v>
+        <v>2.840047374785256e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-2.839918749540013e-06</v>
+        <v>-2.840047374785256e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.194626513796972e-06</v>
+        <v>1.194680620671803e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.194626513796972e-06</v>
+        <v>1.194680620671803e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-7.280963740859724e-07</v>
+        <v>-7.281504809608034e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.715117141175402e-07</v>
+        <v>1.715194822046709e-07</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.715117141175402e-07</v>
+        <v>1.715194822046709e-07</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.715117141175402e-07</v>
+        <v>-1.715194822046709e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.03809333333333333</v>
+        <v>0.0381</v>
       </c>
     </row>
     <row r="10">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.0383047231109061</v>
+        <v>0.03831000088868387</v>
       </c>
     </row>
     <row r="11">
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.03883530459765357</v>
+        <v>0.03883709630935921</v>
       </c>
     </row>
     <row r="12">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-2.726996680290183</v>
+        <v>-2.709079563233819</v>
       </c>
     </row>
     <row r="13">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>63571.67819359694</v>
+        <v>63153.86653210641</v>
       </c>
     </row>
     <row r="15">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9224870.040074628</v>
+        <v>9225287.851736117</v>
       </c>
     </row>
     <row r="17">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>63571.67819359694</v>
+        <v>63153.86653210641</v>
       </c>
     </row>
     <row r="19">
@@ -4791,7 +4791,7 @@
         <v>1000000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3089689.117254046</v>
+        <v>3090106.928915537</v>
       </c>
     </row>
     <row r="21">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>9053787.675606435</v>
+        <v>9054205.487267924</v>
       </c>
     </row>
     <row r="25">
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>9074829.176437067</v>
+        <v>9075246.988098558</v>
       </c>
     </row>
     <row r="28">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>11789933.3682553</v>
+        <v>11790351.17991679</v>
       </c>
     </row>
     <row r="31">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>9053787.675606435</v>
+        <v>9054205.487267924</v>
       </c>
     </row>
     <row r="32">
@@ -5462,16 +5462,16 @@
         <v>5</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.0378</v>
+        <v>0.0377</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.03807250088868387</v>
+        <v>0.03799333422201721</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>335724.3443244282</v>
+        <v>335515.3748822335</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>430797.037474394</v>
+        <v>430588.0680321992</v>
       </c>
     </row>
     <row r="8">
@@ -5805,16 +5805,16 @@
         <v>5</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.038</v>
+        <v>0.0379</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.03823083422201721</v>
+        <v>0.03815166755535054</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>318043.0679807554</v>
+        <v>317834.1303211373</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>406655.2637937185</v>
+        <v>406446.3261341003</v>
       </c>
     </row>
     <row r="15">
@@ -5854,16 +5854,16 @@
         <v>5</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.038</v>
+        <v>0.0379</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.03823083422201721</v>
+        <v>0.03815166755535054</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>316972.0754238004</v>
+        <v>316763.1377641822</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>406050.8030501897</v>
+        <v>405841.8653905716</v>
       </c>
     </row>
     <row r="16">
@@ -5903,16 +5903,16 @@
         <v>5</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.038</v>
+        <v>0.0378</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.03823083422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>316325.6557312972</v>
+        <v>315907.7645221049</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>404941.7943369151</v>
+        <v>404523.9031277228</v>
       </c>
     </row>
     <row r="17">
@@ -5952,16 +5952,16 @@
         <v>5</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.038</v>
+        <v>0.0378</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.03823083422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>319976.6034461427</v>
+        <v>319558.7122369504</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>407259.893438514</v>
+        <v>406842.0022293216</v>
       </c>
     </row>
     <row r="18">
@@ -6001,16 +6001,16 @@
         <v>5</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.038</v>
+        <v>0.0378</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.03823083422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>313995.3772549782</v>
+        <v>313577.4860457859</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>400907.221938702</v>
+        <v>400489.3307295096</v>
       </c>
     </row>
     <row r="19">
@@ -6050,16 +6050,16 @@
         <v>5</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.038</v>
+        <v>0.0378</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.03823083422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>315017.6117457258</v>
+        <v>314599.7205365335</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>401518.3566554659</v>
+        <v>401100.4654462736</v>
       </c>
     </row>
     <row r="20">
@@ -6197,16 +6197,16 @@
         <v>5</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.0379</v>
+        <v>0.0383</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.03815166755535054</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>286823.2598679045</v>
+        <v>287658.915191066</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>375814.8460627886</v>
+        <v>376650.5013859501</v>
       </c>
     </row>
     <row r="23">
@@ -6246,16 +6246,16 @@
         <v>5</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.0379</v>
+        <v>0.0383</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.03815166755535054</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>284233.3436680907</v>
+        <v>285068.9989912522</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>372422.7449528664</v>
+        <v>373258.4002760279</v>
       </c>
     </row>
     <row r="24">
@@ -6295,16 +6295,16 @@
         <v>5</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0379</v>
+        <v>0.0383</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.03815166755535054</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>284096.2031641892</v>
+        <v>284931.8584873506</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>372082.9793193966</v>
+        <v>372918.634642558</v>
       </c>
     </row>
     <row r="25">
@@ -6344,16 +6344,16 @@
         <v>5</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.0379</v>
+        <v>0.0383</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.03815166755535054</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>296587.0507628279</v>
+        <v>297422.7060859893</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>374103.5256415973</v>
+        <v>374939.1809647587</v>
       </c>
     </row>
     <row r="26">
@@ -6393,16 +6393,16 @@
         <v>5</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.0379</v>
+        <v>0.0383</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.03815166755535054</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>296296.2391892042</v>
+        <v>297131.8945123657</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>373763.176233255</v>
+        <v>374598.8315564164</v>
       </c>
     </row>
     <row r="27">
@@ -6589,16 +6589,16 @@
         <v>5</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.0385</v>
+        <v>0.0384</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.03862666755535054</v>
+        <v>0.03854750088868387</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>295303.4437822828</v>
+        <v>295094.5855362514</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>376856.7962464038</v>
+        <v>376647.9380003725</v>
       </c>
     </row>
     <row r="31">
@@ -6638,16 +6638,16 @@
         <v>5</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.0385</v>
+        <v>0.0383</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.03862666755535054</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>296595.0599413526</v>
+        <v>296177.3275713244</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>379049.6001827974</v>
+        <v>378631.8678127691</v>
       </c>
     </row>
     <row r="32">
@@ -6687,16 +6687,16 @@
         <v>5</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>0.0385</v>
+        <v>0.0383</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.03862666755535054</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>295174.3904631064</v>
+        <v>294756.6580930781</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>377387.2216843806</v>
+        <v>376969.4893143523</v>
       </c>
     </row>
     <row r="33">
@@ -6736,16 +6736,16 @@
         <v>5</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.0385</v>
+        <v>0.0383</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.03862666755535054</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>295174.7499935334</v>
+        <v>294757.0176235051</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>377358.1558285666</v>
+        <v>376940.4234585383</v>
       </c>
     </row>
     <row r="34">
@@ -6865,10 +6865,10 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" s="12" t="n">
-        <v>9224870.040074628</v>
+        <v>9225287.851736117</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>11789933.3682553</v>
+        <v>11790351.17991679</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
+++ b/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8938388.0890132</v>
+        <v>9054205.487267924</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>8959429.589843834</v>
+        <v>9075246.988098558</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>8938388.0890132</v>
+        <v>9054205.487267924</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
-        <v>11674533.78166207</v>
+        <v>11790351.17991679</v>
       </c>
     </row>
     <row r="19">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-8938388.0890132</v>
+        <v>-9054205.487267924</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1359765.813551093</v>
+        <v>1243948.415296367</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-20T09:02:29+00:00</t>
+          <t>2026-07-31T00:23:57+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3016814.344352271</v>
+        <v>3055169.986446361</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3016814.344352271</v>
+        <v>3055169.986446361</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>9859.226910800955</v>
+        <v>-28496.41518328837</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1346107.837428922</v>
+        <v>1363222.192022578</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1346107.837428922</v>
+        <v>1363222.192022578</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>-1346107.837428922</v>
+        <v>-1363222.192022578</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1123596.569266267</v>
+        <v>1137881.925589106</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1123596.569266267</v>
+        <v>1137881.925589106</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-25108.40012026665</v>
+        <v>-39393.75644310547</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>884593.715699312</v>
+        <v>895840.4004751126</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>884593.715699312</v>
+        <v>895840.4004751126</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>111852.7041399166</v>
+        <v>100606.019364116</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>156917846.5942976</v>
@@ -1137,13 +1137,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>579178.9336724702</v>
+        <v>586542.5886252404</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>579178.9336724702</v>
+        <v>586542.5886252404</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>985466.0663275338</v>
+        <v>978102.4113747637</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>400430.4104066796</v>
+        <v>405521.4646619409</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>400430.4104066796</v>
+        <v>405521.4646619409</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>113372.8935789841</v>
+        <v>108281.8393237228</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>89993374.27336854</v>
@@ -1271,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>325101.0963526713</v>
+        <v>329234.4170919614</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>289705.209878071</v>
+        <v>293838.5306173611</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>93414.59926042407</v>
+        <v>89281.27852113397</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>313001.7760726303</v>
+        <v>316981.2665972398</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>278923.221873611</v>
+        <v>282902.7123982206</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>80301.82937660547</v>
+        <v>76322.3388519959</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1401,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>283882.8341881231</v>
+        <v>287492.1077932952</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>252974.6499840619</v>
+        <v>256583.9235892341</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>68335.14510265466</v>
+        <v>64725.87149748252</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>237652.8026041482</v>
+        <v>240674.3096638738</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>237652.8026041482</v>
+        <v>240674.3096638738</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>177441.3805831652</v>
+        <v>174419.8735234396</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>226133.7174256953</v>
+        <v>229008.7713537646</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>226133.7174256953</v>
+        <v>229008.7713537646</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-199366.3784786953</v>
+        <v>-202241.4324067646</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>218592.6026774182</v>
+        <v>221371.7792112366</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>218592.6026774182</v>
+        <v>221371.7792112366</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-188466.458157086</v>
+        <v>-191245.6346909044</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1722,13 +1722,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>44521.89635512782</v>
+        <v>45087.94574598421</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>44521.89635512782</v>
+        <v>45087.94574598421</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>51125.42333508717</v>
+        <v>50559.37394423078</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>27137.96422153645</v>
+        <v>27482.99507992921</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>27137.96422153645</v>
+        <v>27482.99507992921</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>10216.38215446355</v>
+        <v>9871.351296070787</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1852,13 +1852,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>25275.14494069606</v>
+        <v>25596.49199840826</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>25275.14494069606</v>
+        <v>25596.49199840826</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>18870.94302655907</v>
+        <v>18549.59596884687</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>10973.53805739011</v>
+        <v>11113.05512744882</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>10973.53805739011</v>
+        <v>11113.05512744882</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-10973.53805739011</v>
+        <v>-11113.05512744882</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2051,13 +2051,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>10924.52721324161</v>
+        <v>11063.42116162881</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>10924.52721324161</v>
+        <v>11063.42116162881</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-10924.52721324161</v>
+        <v>-11063.42116162881</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2116,13 +2116,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>10914.128040777</v>
+        <v>11052.8897745525</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>10914.128040777</v>
+        <v>11052.8897745525</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-10914.128040777</v>
+        <v>-11052.8897745525</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2181,13 +2181,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>10876.08723410139</v>
+        <v>11014.36531876916</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>10876.08723410139</v>
+        <v>11014.36531876916</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-10876.08723410139</v>
+        <v>-11014.36531876916</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2246,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>10019.95487495214</v>
+        <v>10147.34813125313</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>8929.016735359764</v>
+        <v>9056.409991660761</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-7151.348503144608</v>
+        <v>-7278.741759445605</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3301.209816188345</v>
+        <v>3343.181249539641</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3301.209816188345</v>
+        <v>3343.181249539641</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1609.906525296875</v>
+        <v>1567.935091945579</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2445,13 +2445,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>437.1879644036105</v>
+        <v>442.7463525496694</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>437.1879644036105</v>
+        <v>442.7463525496694</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>253.1499120251614</v>
+        <v>247.5915238791025</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2579,13 +2579,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>1.22083778650683</v>
+        <v>1.236359463298728</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.22083778650683</v>
+        <v>1.236359463298728</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>96.39293745732098</v>
+        <v>96.37741578052908</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2644,13 +2644,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.6419890530752891</v>
+        <v>0.650151273065451</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.6419890530752891</v>
+        <v>0.650151273065451</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.6419890530752891</v>
+        <v>-0.650151273065451</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2709,13 +2709,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.225711558019194</v>
+        <v>0.2285812446315275</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.225711558019194</v>
+        <v>0.2285812446315275</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08505713068635073</v>
+        <v>0.08218744407401721</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2774,13 +2774,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.04953909970085183</v>
+        <v>0.05016893758973168</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.04953909970085183</v>
+        <v>0.05016893758973168</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.04935510306793594</v>
+        <v>-0.04998494095681579</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2839,13 +2839,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.02264960684745605</v>
+        <v>0.02293757293175926</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.02264960684745605</v>
+        <v>0.02293757293175926</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-8.685264606847456</v>
+        <v>-8.685552572931758</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.01337190451591287</v>
+        <v>0.01354191430941868</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.01337190451591287</v>
+        <v>0.01354191430941868</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.001804904515912871</v>
+        <v>-0.001974914309418679</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2969,13 +2969,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.0003508812847691781</v>
+        <v>0.0003553423736662512</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.0003508812847691781</v>
+        <v>0.0003553423736662512</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>9.111871523082189e-05</v>
+        <v>8.665762633374878e-05</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3034,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.0001310877916848805</v>
+        <v>0.0001327544359814321</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.0001310877916848805</v>
+        <v>0.0001327544359814321</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>2.791220831511948e-05</v>
+        <v>2.624556401856786e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3099,13 +3099,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.438892543412677e-05</v>
+        <v>1.457186558591407e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.438892543412677e-05</v>
+        <v>1.457186558591407e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-2.388925434126771e-06</v>
+        <v>-2.57186558591407e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.299464221073062e-05</v>
+        <v>1.315985550823055e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.299464221073062e-05</v>
+        <v>1.315985550823055e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.180289284417862e-05</v>
+        <v>-1.196810614167855e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>3.855589794937317e-06</v>
+        <v>3.904609590442164e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>3.855589794937317e-06</v>
+        <v>3.904609590442164e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.444102050626837e-07</v>
+        <v>9.539040955783619e-08</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>2.804392455052222e-06</v>
+        <v>2.840047374785256e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>2.804392455052222e-06</v>
+        <v>2.840047374785256e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-2.804392455052222e-06</v>
+        <v>-2.840047374785256e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.179682194231862e-06</v>
+        <v>1.194680620671803e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.179682194231862e-06</v>
+        <v>1.194680620671803e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-7.13152054520862e-07</v>
+        <v>-7.281504809608034e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.693661683462633e-07</v>
+        <v>1.715194822046709e-07</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.693661683462633e-07</v>
+        <v>1.715194822046709e-07</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.693661683462633e-07</v>
+        <v>-1.715194822046709e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -4687,11 +4687,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reference rate (effr), period avg</t>
+          <t>Reference rate (tbill_3m), period avg</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.03625333333333333</v>
+        <v>0.0381</v>
       </c>
     </row>
     <row r="10">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.03684805644423943</v>
+        <v>0.03831000088868387</v>
       </c>
     </row>
     <row r="11">
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.03834079216689766</v>
+        <v>0.03883709630935921</v>
       </c>
     </row>
     <row r="12">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-7.67212098784927</v>
+        <v>-2.709079563233819</v>
       </c>
     </row>
     <row r="13">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>178971.2647868314</v>
+        <v>63153.86653210641</v>
       </c>
     </row>
     <row r="15">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9109470.453481393</v>
+        <v>9225287.851736117</v>
       </c>
     </row>
     <row r="17">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>178971.2647868314</v>
+        <v>63153.86653210641</v>
       </c>
     </row>
     <row r="19">
@@ -4791,7 +4791,7 @@
         <v>1000000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2974289.530660812</v>
+        <v>3090106.928915537</v>
       </c>
     </row>
     <row r="21">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>8938388.0890132</v>
+        <v>9054205.487267924</v>
       </c>
     </row>
     <row r="25">
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>8959429.589843834</v>
+        <v>9075246.988098558</v>
       </c>
     </row>
     <row r="28">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>11674533.78166207</v>
+        <v>11790351.17991679</v>
       </c>
     </row>
     <row r="31">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>8938388.0890132</v>
+        <v>9054205.487267924</v>
       </c>
     </row>
     <row r="32">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>effr</t>
+          <t>tbill_3m</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         <v>5</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>328871.5443734901</v>
+        <v>332216.9641822214</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>422088.5384580736</v>
+        <v>425433.9582668049</v>
       </c>
     </row>
     <row r="7">
@@ -5462,16 +5462,16 @@
         <v>5</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0377</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03799333422201721</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>332378.924515697</v>
+        <v>335515.3748822335</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>427451.6176656627</v>
+        <v>430588.0680321992</v>
       </c>
     </row>
     <row r="8">
@@ -5511,16 +5511,16 @@
         <v>5</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>331720.0698500753</v>
+        <v>335065.4896588066</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>426488.7538702118</v>
+        <v>429834.173678943</v>
       </c>
     </row>
     <row r="9">
@@ -5560,16 +5560,16 @@
         <v>5</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>326047.8655439609</v>
+        <v>329393.2853526921</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>417263.8473377806</v>
+        <v>420609.2671465119</v>
       </c>
     </row>
     <row r="10">
@@ -5609,16 +5609,16 @@
         <v>5</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>319406.0428190686</v>
+        <v>322751.4626277998</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>399742.1334906419</v>
+        <v>403087.5532993731</v>
       </c>
     </row>
     <row r="11">
@@ -5658,16 +5658,16 @@
         <v>5</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>320043.8191133141</v>
+        <v>323389.2389220453</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>403809.4229262104</v>
+        <v>407154.8427349417</v>
       </c>
     </row>
     <row r="12">
@@ -5707,16 +5707,16 @@
         <v>5</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>322496.4212176412</v>
+        <v>325841.8410263725</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>408436.9319920092</v>
+        <v>411782.3518007405</v>
       </c>
     </row>
     <row r="13">
@@ -5756,16 +5756,16 @@
         <v>5</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.038</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03823083422201721</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>316249.7906001595</v>
+        <v>320013.1016180831</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>405540.7609192973</v>
+        <v>409304.0719372209</v>
       </c>
     </row>
     <row r="14">
@@ -5805,16 +5805,16 @@
         <v>5</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0379</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03815166755535054</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>314279.7569628318</v>
+        <v>317834.1303211373</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>402891.9527757948</v>
+        <v>406446.3261341003</v>
       </c>
     </row>
     <row r="15">
@@ -5854,16 +5854,16 @@
         <v>5</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0379</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03815166755535054</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>313208.7644058768</v>
+        <v>316763.1377641822</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>402287.4920322661</v>
+        <v>405841.8653905716</v>
       </c>
     </row>
     <row r="16">
@@ -5903,16 +5903,16 @@
         <v>5</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>312562.3447133736</v>
+        <v>315907.7645221049</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>401178.4833189916</v>
+        <v>404523.9031277228</v>
       </c>
     </row>
     <row r="17">
@@ -5952,16 +5952,16 @@
         <v>5</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>316213.2924282191</v>
+        <v>319558.7122369504</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>403496.5824205904</v>
+        <v>406842.0022293216</v>
       </c>
     </row>
     <row r="18">
@@ -6001,16 +6001,16 @@
         <v>5</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>310232.0662370546</v>
+        <v>313577.4860457859</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>397143.9109207783</v>
+        <v>400489.3307295096</v>
       </c>
     </row>
     <row r="19">
@@ -6050,16 +6050,16 @@
         <v>5</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.03680583422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>311254.3007278022</v>
+        <v>314599.7205365335</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>397755.0456375423</v>
+        <v>401100.4654462736</v>
       </c>
     </row>
     <row r="20">
@@ -6099,16 +6099,16 @@
         <v>5</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0379</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03815166755535054</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>312580.8845328511</v>
+        <v>315926.0497723278</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>400228.3688737685</v>
+        <v>403573.5341132453</v>
       </c>
     </row>
     <row r="21">
@@ -6148,16 +6148,16 @@
         <v>5</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0379</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03815166755535054</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>283943.509511777</v>
+        <v>287288.6747512537</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>371609.9739917676</v>
+        <v>374955.1392312443</v>
       </c>
     </row>
     <row r="22">
@@ -6197,16 +6197,16 @@
         <v>5</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0383</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>283478.0946284278</v>
+        <v>287658.915191066</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>372469.6808233119</v>
+        <v>376650.5013859501</v>
       </c>
     </row>
     <row r="23">
@@ -6246,16 +6246,16 @@
         <v>5</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0383</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>280888.178428614</v>
+        <v>285068.9989912522</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>369077.5797133897</v>
+        <v>373258.4002760279</v>
       </c>
     </row>
     <row r="24">
@@ -6295,16 +6295,16 @@
         <v>5</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0383</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>280751.0379247125</v>
+        <v>284931.8584873506</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>368737.8140799199</v>
+        <v>372918.634642558</v>
       </c>
     </row>
     <row r="25">
@@ -6344,16 +6344,16 @@
         <v>5</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0383</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>293241.8855233512</v>
+        <v>297422.7060859893</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>370758.3604021206</v>
+        <v>374939.1809647587</v>
       </c>
     </row>
     <row r="26">
@@ -6393,16 +6393,16 @@
         <v>5</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0383</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>292951.0739497275</v>
+        <v>297131.8945123657</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>370418.0109937783</v>
+        <v>374598.8315564164</v>
       </c>
     </row>
     <row r="27">
@@ -6442,16 +6442,16 @@
         <v>5</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0385</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03862666755535054</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>292903.485130229</v>
+        <v>297502.0380628955</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>368775.8833457375</v>
+        <v>373374.436278404</v>
       </c>
     </row>
     <row r="28">
@@ -6491,16 +6491,16 @@
         <v>5</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0385</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03862666755535054</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>292540.025103776</v>
+        <v>297138.5780364425</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>367768.4940876255</v>
+        <v>372367.0470202919</v>
       </c>
     </row>
     <row r="29">
@@ -6540,16 +6540,16 @@
         <v>5</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0385</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03862666755535054</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>289224.3159347967</v>
+        <v>293822.8688674631</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>365031.4634654266</v>
+        <v>369630.016398093</v>
       </c>
     </row>
     <row r="30">
@@ -6589,16 +6589,16 @@
         <v>5</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0384</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03854750088868387</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>290704.8908496163</v>
+        <v>295094.5855362514</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>372258.2433137374</v>
+        <v>376647.9380003725</v>
       </c>
     </row>
     <row r="31">
@@ -6638,16 +6638,16 @@
         <v>5</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0383</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>291996.5070086862</v>
+        <v>296177.3275713244</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>374451.047250131</v>
+        <v>378631.8678127691</v>
       </c>
     </row>
     <row r="32">
@@ -6687,16 +6687,16 @@
         <v>5</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0383</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>290575.83753044</v>
+        <v>294756.6580930781</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>372788.6687517141</v>
+        <v>376969.4893143523</v>
       </c>
     </row>
     <row r="33">
@@ -6736,16 +6736,16 @@
         <v>5</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0383</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>290576.1970608669</v>
+        <v>294757.0176235051</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>372759.6028959002</v>
+        <v>376940.4234585383</v>
       </c>
     </row>
     <row r="34">
@@ -6785,16 +6785,16 @@
         <v>5</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0387</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03878500088868388</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>289071.3915046069</v>
+        <v>294087.6133054312</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>370536.1472642949</v>
+        <v>375552.3690651191</v>
       </c>
     </row>
     <row r="35">
@@ -6834,16 +6834,16 @@
         <v>5</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0387</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.03688500088868387</v>
+        <v>0.03878500088868388</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>279078.1353503489</v>
+        <v>284094.3571511732</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>371288.9686435931</v>
+        <v>376305.1904444174</v>
       </c>
     </row>
     <row r="37">
@@ -6865,10 +6865,10 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" s="12" t="n">
-        <v>9109470.453481393</v>
+        <v>9225287.851736117</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>11674533.78166207</v>
+        <v>11790351.17991679</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
+++ b/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1650764.59</v>
+        <v>1648334.12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>13045268.95174489</v>
+        <v>13042838.48174489</v>
       </c>
     </row>
     <row r="9">

--- a/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
+++ b/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
@@ -4677,7 +4677,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Base rate (BR = SSR + 30bps), period avg</t>
+          <t>Base rate (BR = SSR (+) spread; 30bps, 20bps from 2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
@@ -4896,7 +4896,7 @@
     <row r="35" ht="60" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
+          <t>sUSDS spread (Curve LP + PSM3) — the BR−SSR spread (30 bps; 20 bps from 2026-07-23) × value, integrated daily, deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + spread nets to zero economically.</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>tbill_3m</t>
+          <t>tbill_3m→sofr@2026-07-23</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
+          <t>Base rate composition: base_apy = (1 + SSR)(1 + spread) − 1 (multiplicative; spread 30bps, 20bps from 2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+spread)−1 (multiplicative; spread 30bps, 20bps from 2026-07-23). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
+++ b/settlements/spark/2026-06/spark_settlement_june_2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>11279641.55178227</v>
+        <v>11315564.9652411</v>
       </c>
     </row>
     <row r="5">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>114862.809962623</v>
+        <v>115023.434120822</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>13042838.48174489</v>
+        <v>13078922.51936193</v>
       </c>
     </row>
     <row r="9">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>9054205.487267924</v>
+        <v>9107813.391973251</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>9075246.988098558</v>
+        <v>9128854.892803885</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9054205.487267924</v>
+        <v>9107813.391973251</v>
       </c>
     </row>
     <row r="16">
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-2736145.692648868</v>
+        <v>-2740055.004884402</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
-        <v>11790351.17991679</v>
+        <v>11847868.39685765</v>
       </c>
     </row>
     <row r="19">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>171082.3644681933</v>
+        <v>171338.1568180806</v>
       </c>
     </row>
     <row r="21">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>11279641.55178227</v>
+        <v>11315564.9652411</v>
       </c>
     </row>
     <row r="23">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-9054205.487267924</v>
+        <v>-9107813.391973251</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1243948.415296367</v>
+        <v>1226008.131699994</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-31T00:23:57+00:00</t>
+          <t>2026-09-01T17:39:12+00:00</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S64"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -855,13 +855,13 @@
         <v>-399728271.1675428</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>3026673.571263072</v>
+        <v>3026673.571263095</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>3026673.571263072</v>
+        <v>3026673.571263095</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3055169.986446361</v>
+        <v>3058609.571656722</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3055169.986446361</v>
+        <v>3058609.571656722</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-28496.41518328837</v>
+        <v>-31936.0003936264</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1363222.192022578</v>
+        <v>1364756.940959926</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1363222.192022578</v>
+        <v>1364756.940959926</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>-1363222.192022578</v>
+        <v>-1364756.940959926</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1137881.925589106</v>
+        <v>1139162.980934555</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1137881.925589106</v>
+        <v>1139162.980934555</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>-39393.75644310547</v>
+        <v>-40674.81178855478</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>895840.4004751126</v>
+        <v>896848.9595425255</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>895840.4004751126</v>
+        <v>896848.9595425255</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>100606.019364116</v>
+        <v>99597.46029670317</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>156917846.5942976</v>
@@ -1119,13 +1119,13 @@
         <v>-26207983.366548</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1564645.000000004</v>
+        <v>1564644.999999998</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>1564645.000000004</v>
+        <v>1564644.999999998</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>586542.5886252404</v>
+        <v>587202.9326394956</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>586542.5886252404</v>
+        <v>587202.9326394956</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>978102.4113747637</v>
+        <v>977442.0673605024</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>405521.4646619409</v>
+        <v>405978.0106605344</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>405521.4646619409</v>
+        <v>405978.0106605344</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>108281.8393237228</v>
+        <v>107825.2933251293</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>89993374.27336854</v>
@@ -1271,19 +1271,19 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>329234.4170919614</v>
+        <v>329605.0772636688</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>293838.5306173611</v>
+        <v>294156.2689288532</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>89281.27852113397</v>
+        <v>88910.61834942662</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>35395.88647460032</v>
+        <v>35448.80833481559</v>
       </c>
       <c r="S8" t="inlineStr"/>
     </row>
@@ -1336,19 +1336,19 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>316981.2665972398</v>
+        <v>317338.1318719664</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>282902.7123982206</v>
+        <v>283208.6254109391</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>76322.3388519959</v>
+        <v>75965.47357726938</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>34078.55419901927</v>
+        <v>34129.50646102725</v>
       </c>
       <c r="S9" t="inlineStr"/>
     </row>
@@ -1401,19 +1401,19 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>287492.1077932952</v>
+        <v>287815.7734506721</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>256583.9235892341</v>
+        <v>256861.3771364798</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>64725.87149748252</v>
+        <v>64402.20584010562</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>30908.18420406113</v>
+        <v>30954.39631419231</v>
       </c>
       <c r="S10" t="inlineStr"/>
     </row>
@@ -1466,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>240674.3096638738</v>
+        <v>240945.2666972651</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>240674.3096638738</v>
+        <v>240945.2666972651</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>174419.8735234396</v>
+        <v>174148.9164900483</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>229008.7713537646</v>
+        <v>229266.5950383667</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>229008.7713537646</v>
+        <v>229266.5950383667</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-202241.4324067646</v>
+        <v>-202499.2560913667</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>221371.7792112366</v>
+        <v>221621.0049830084</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>221371.7792112366</v>
+        <v>221621.0049830084</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-191245.6346909044</v>
+        <v>-191494.8604626762</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1656,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>-69608.80145092019</v>
+        <v>-69712.87646152294</v>
       </c>
       <c r="P14" s="6" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>69608.80145092019</v>
+        <v>69712.87646152294</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1722,13 +1722,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>45087.94574598421</v>
+        <v>45138.70685978195</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>45087.94574598421</v>
+        <v>45138.70685978195</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>50559.37394423078</v>
+        <v>50508.61283043304</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1741,12 +1741,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S65</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spark USDC (SparkLend spToken)</t>
+          <t>Spark Blue Chip USDT Vault (Morpho — 2026-06 redeployment)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1756,44 +1756,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>12183497.214187</v>
+        <v>0</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>6740456.351987</v>
+        <v>45918530.85783745</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-5443040.8622</v>
+        <v>45918530.85783745</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>37354.346376</v>
+        <v>35923.41345892701</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>37354.346376</v>
+        <v>35923.41345892701</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>12000817.37390113</v>
+        <v>18963744.02866561</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>27482.99507992921</v>
+        <v>43477.64200854699</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>27482.99507992921</v>
+        <v>43477.64200854699</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>9871.351296070787</v>
+        <v>-7554.228549619987</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
+          <t>Spark USDC (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1821,44 +1821,44 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>71943502.10038626</v>
+        <v>12183497.214187</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1.753936570309431</v>
+        <v>6740456.351987</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-71943500.34644969</v>
+        <v>-5443040.8622</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>44146.08796725513</v>
+        <v>37354.346376</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>44146.08796725513</v>
+        <v>37354.346376</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>11177050.57225555</v>
+        <v>12000817.37390113</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>25596.49199840826</v>
+        <v>27513.93610901523</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>25596.49199840826</v>
+        <v>27513.93610901523</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>18549.59596884687</v>
+        <v>9840.410266984774</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1871,12 +1871,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>Spark Blue Chip USDT Vault (Morpho — pre-2026-06 deployment)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1886,136 +1886,136 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>48750265.64989898</v>
+        <v>71943502.10038626</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.823120129440027</v>
+        <v>1.753936570309431</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-48750264.82677885</v>
+        <v>-71943500.34644969</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>19891.47439593931</v>
+        <v>44146.08796725314</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>11483.07201201587</v>
+        <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>11483.07201201587</v>
+        <v>44146.08796725314</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>19891.47439593931</v>
+        <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>47124211.00412609</v>
+        <v>11177050.57225555</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0</v>
+        <v>25625.30915611321</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>19891.47439593931</v>
+        <v>25625.30915611321</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>11483.07201201587</v>
+        <v>18520.77881113993</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>47124211.00412609</v>
+        <v>0</v>
       </c>
       <c r="R18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>5019997.4</v>
+        <v>48750265.64989898</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0</v>
+        <v>0.823120129440027</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-5019997.4</v>
+        <v>-48750264.82677885</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0</v>
+        <v>19891.47439593931</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0</v>
+        <v>11483.07201201587</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0</v>
+        <v>11483.07201201587</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0</v>
+        <v>19891.47439593931</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>4852664.153333333</v>
+        <v>47124211.00412609</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>11113.05512744882</v>
+        <v>0</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>11113.05512744882</v>
+        <v>19891.47439593931</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-11113.05512744882</v>
+        <v>11483.07201201587</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0</v>
+        <v>47124211.00412609</v>
       </c>
       <c r="R19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2024,13 +2024,13 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>4997576.708614</v>
+        <v>5019997.4</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-4997576.708614</v>
+        <v>-5019997.4</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>0</v>
@@ -2045,19 +2045,19 @@
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>4830990.818326866</v>
+        <v>4852664.153333333</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>11063.42116162881</v>
+        <v>11125.56647713734</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>11063.42116162881</v>
+        <v>11125.56647713734</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-11063.42116162881</v>
+        <v>-11125.56647713734</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2070,17 +2070,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2089,13 +2089,13 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>4992819.462732</v>
+        <v>4997576.708614</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-4992819.462732</v>
+        <v>-4997576.708614</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>0</v>
@@ -2110,19 +2110,19 @@
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4826392.1473076</v>
+        <v>4830990.818326866</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11052.8897745525</v>
+        <v>11075.87663218277</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11052.8897745525</v>
+        <v>11075.87663218277</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11052.8897745525</v>
+        <v>-11075.87663218277</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2135,17 +2135,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>4975417.167355</v>
+        <v>4992819.462732</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-4975417.167355</v>
+        <v>-4992819.462732</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>0</v>
@@ -2175,19 +2175,19 @@
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>4809569.928443166</v>
+        <v>4826392.1473076</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11014.36531876916</v>
+        <v>11065.33338861291</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11014.36531876916</v>
+        <v>11065.33338861291</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11014.36531876916</v>
+        <v>-11065.33338861291</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2200,82 +2200,82 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>985396.9281006901</v>
+        <v>4975417.167355</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>104355616.018357</v>
+        <v>0</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>103370219.0902563</v>
+        <v>-4975417.167355</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2868.606371807529</v>
+        <v>0</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>2868.606371807529</v>
+        <v>0</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>4430975.277563506</v>
+        <v>4809569.928443166</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>10147.34813125313</v>
+        <v>11026.76556105356</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>9056.409991660761</v>
+        <v>11026.76556105356</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-7278.741759445605</v>
+        <v>-11026.76556105356</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>1090.938139592373</v>
+        <v>0</v>
       </c>
       <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDC Vault (Morpho)</t>
+          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2284,58 +2284,58 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>3501087.141508509</v>
+        <v>985396.9281006901</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>640616.8200220506</v>
+        <v>104355616.018357</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>-2860470.321486458</v>
+        <v>103370219.0902563</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>4911.11634148522</v>
+        <v>2868.606371807529</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>4911.11634148522</v>
+        <v>2868.606371807529</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>1459844.806102522</v>
+        <v>4430975.277563506</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3343.181249539641</v>
+        <v>10158.77226434932</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3343.181249539641</v>
+        <v>9066.203017826814</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1567.935091945579</v>
+        <v>-7290.165892541792</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>0</v>
+        <v>1092.569246522508</v>
       </c>
       <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S61</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Uniswap V4 (PYUSD/USDS)</t>
+          <t>Spark Blue Chip USDC Vault (Morpho)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2345,200 +2345,196 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>220002.6507685304</v>
+        <v>3501087.141508509</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>100119969.930802</v>
+        <v>640616.8200220506</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>99899967.28003348</v>
+        <v>-2860470.321486458</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>1030.276249266686</v>
+        <v>4911.11634135129</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0</v>
+        <v>4911.11634135129</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>1030.276249266686</v>
+        <v>0</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>22121073.51134836</v>
+        <v>1459844.806102652</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0</v>
+        <v>3346.945084885431</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>1030.276249266686</v>
+        <v>3346.945084885431</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0</v>
+        <v>1564.171256465859</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>22121073.51134836</v>
+        <v>0</v>
       </c>
       <c r="R25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S61</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>Spark.fi PYUSD Reserve Uniswap V4 (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>424.9110349025811</v>
+        <v>220002.6507685304</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>394.3129623374141</v>
+        <v>100119969.930802</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-30.59807256516697</v>
+        <v>99899967.28003348</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>690.3378764287719</v>
+        <v>1030.276249266686</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>690.3378764287719</v>
+        <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0</v>
+        <v>1030.276249266686</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>193331.1163669253</v>
+        <v>22121073.51134836</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>442.7463525496694</v>
+        <v>0</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>442.7463525496694</v>
+        <v>1030.276249266686</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>247.5915238791025</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>0</v>
+        <v>22121073.51134836</v>
       </c>
       <c r="R26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S62</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Uniswap V4 (USDT/USDS)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>1250066.267840007</v>
+        <v>424.9110349025811</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>50000000.01256605</v>
+        <v>394.3129623374141</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>48749933.74472605</v>
+        <v>-30.59807256516697</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>119.7501854271759</v>
+        <v>690.3378764314629</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0</v>
+        <v>690.3378764314629</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>119.7501854271759</v>
+        <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>18435553.22634522</v>
+        <v>193331.1163669235</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0</v>
+        <v>443.244807238906</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>119.7501854271759</v>
+        <v>443.244807238906</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0</v>
+        <v>247.0930691925569</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>18435553.22634522</v>
+        <v>0</v>
       </c>
       <c r="R27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S62</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>Spark.fi USDT Reserve Uniswap V4 (USDT/USDS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2548,67 +2544,71 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>539.8728953809741</v>
+        <v>1250066.267840007</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>637.4866706248019</v>
+        <v>50000000.01256605</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>97.6137752438278</v>
+        <v>48749933.74472605</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>97.6137752438278</v>
+        <v>119.7501854271759</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>97.6137752438278</v>
+        <v>0</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0</v>
+        <v>119.7501854271759</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>539.8728953809741</v>
+        <v>18435553.22634522</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>1.236359463298728</v>
+        <v>0</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.236359463298728</v>
+        <v>119.7501854271759</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>96.37741578052908</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>0</v>
+        <v>18435553.22634522</v>
       </c>
       <c r="R28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2617,40 +2617,40 @@
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>539.8728953809741</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>637.4866706248019</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0</v>
+        <v>97.6137752438278</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0</v>
+        <v>97.6137752438278</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0</v>
+        <v>97.6137752438278</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>539.8728953809741</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.650151273065451</v>
+        <v>1.237751387068442</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.650151273065451</v>
+        <v>1.237751387068442</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.650151273065451</v>
+        <v>96.37602385675936</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2663,17 +2663,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2682,40 +2682,40 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>99.81305763596731</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>100.1238263246728</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.3107686887055447</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.3107686887055447</v>
+        <v>0</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.3107686887055447</v>
+        <v>0</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>99.81305763596731</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2285812446315275</v>
+        <v>0.650883229294811</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2285812446315275</v>
+        <v>0.650883229294811</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08218744407401721</v>
+        <v>-0.650883229294811</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2728,12 +2728,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2747,40 +2747,40 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>21.90661272343654</v>
+        <v>99.81305763596731</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>21.90842102645718</v>
+        <v>100.1238263246728</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.001808303020639377</v>
+        <v>0.3107686887055447</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.0001839966329158897</v>
+        <v>0.3107686887055447</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.0001839966329158897</v>
+        <v>0.3107686887055447</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>21.90693758471409</v>
+        <v>99.81305763596731</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.05016893758973168</v>
+        <v>0.228838586996073</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.05016893758973168</v>
+        <v>0.228838586996073</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.04998494095681579</v>
+        <v>0.08193010170947171</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2793,12 +2793,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2808,44 +2808,44 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>10.015998</v>
+        <v>21.90661272343654</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1.353383</v>
+        <v>21.90842102645718</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-8.662615000000001</v>
+        <v>0.001808303020639377</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-8.662615000000001</v>
+        <v>0.0001839966329158897</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>-8.662615000000001</v>
+        <v>0.0001839966329158897</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>10.015998</v>
+        <v>21.90693758471409</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.02293757293175926</v>
+        <v>0.05022541900861138</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.02293757293175926</v>
+        <v>0.05022541900861138</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-8.685552572931758</v>
+        <v>-0.05004142237569549</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2858,12 +2858,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2873,44 +2873,44 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>5.913258</v>
+        <v>10.015998</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>5.924825</v>
+        <v>1.353383</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.011567</v>
+        <v>-8.662615000000001</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.011567</v>
+        <v>-8.662615000000001</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.011567</v>
+        <v>-8.662615000000001</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>5.913258</v>
+        <v>10.015998</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.01354191430941868</v>
+        <v>0.02296339661324594</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.01354191430941868</v>
+        <v>0.02296339661324594</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.001974914309418679</v>
+        <v>-8.685578396613247</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2923,17 +2923,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2942,40 +2942,40 @@
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0.155165</v>
+        <v>5.913258</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.155607</v>
+        <v>5.924825</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.000442</v>
+        <v>0.011567</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.000442</v>
+        <v>0.011567</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.000442</v>
+        <v>0.011567</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.155165</v>
+        <v>5.913258</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.0003553423736662512</v>
+        <v>0.01355716012827174</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.0003553423736662512</v>
+        <v>0.01355716012827174</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>8.665762633374878e-05</v>
+        <v>-0.001990160128271735</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2988,17 +2988,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3007,40 +3007,40 @@
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>0.057969</v>
+        <v>0.155165</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.058128</v>
+        <v>0.155607</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.000159</v>
+        <v>0.000442</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.000159</v>
+        <v>0.000442</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.000159</v>
+        <v>0.000442</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.057969</v>
+        <v>0.155165</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.0001327544359814321</v>
+        <v>0.0003557424268150119</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.0001327544359814321</v>
+        <v>0.0003557424268150119</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>2.624556401856786e-05</v>
+        <v>8.625757318498808e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3053,17 +3053,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3072,40 +3072,40 @@
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.006363</v>
+        <v>0.057969</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.006375</v>
+        <v>0.058128</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>1.2e-05</v>
+        <v>0.000159</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>1.2e-05</v>
+        <v>0.000159</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>1.2e-05</v>
+        <v>0.000159</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.006363</v>
+        <v>0.057969</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.457186558591407e-05</v>
+        <v>0.0001329038941774203</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.457186558591407e-05</v>
+        <v>0.0001329038941774203</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-2.57186558591407e-06</v>
+        <v>2.609610582257967e-05</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3118,17 +3118,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3137,40 +3137,40 @@
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>0.005746426914602806</v>
+        <v>0.006363</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.005747618663969358</v>
+        <v>0.006375</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>1.191749366552e-06</v>
+        <v>1.2e-05</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>1.191749366552e-06</v>
+        <v>1.2e-05</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>1.191749366552e-06</v>
+        <v>1.2e-05</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.005746426914602806</v>
+        <v>0.006363</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.315985550823055e-05</v>
+        <v>1.458827094914395e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.315985550823055e-05</v>
+        <v>1.458827094914395e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.196810614167855e-05</v>
+        <v>-2.588270949143949e-06</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3183,17 +3183,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3202,40 +3202,40 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.001705</v>
+        <v>0.005746426914602806</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.001709</v>
+        <v>0.005747618663969358</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>4e-06</v>
+        <v>1.191749366552e-06</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>4e-06</v>
+        <v>1.191749366552e-06</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>4e-06</v>
+        <v>1.191749366552e-06</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.001705</v>
+        <v>0.005746426914602806</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>3.904609590442164e-06</v>
+        <v>1.317467119592629e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>3.904609590442164e-06</v>
+        <v>1.317467119592629e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>9.539040955783619e-08</v>
+        <v>-1.198292182937429e-05</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3248,59 +3248,59 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.001705</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.001709</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.001705</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>2.840047374785256e-06</v>
+        <v>3.909005495566625e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>2.840047374785256e-06</v>
+        <v>3.909005495566625e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-2.840047374785256e-06</v>
+        <v>9.09945044333753e-08</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3313,12 +3313,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3328,44 +3328,44 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.000521673271312833</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.000522139801452544</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>4.66530139711e-07</v>
+        <v>0</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>4.66530139711e-07</v>
+        <v>0</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>4.66530139711e-07</v>
+        <v>0</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.000521673271312833</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.194680620671803e-06</v>
+        <v>2.843244769689753e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.194680620671803e-06</v>
+        <v>2.843244769689753e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-7.281504809608034e-07</v>
+        <v>-2.843244769689753e-06</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3378,12 +3378,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3393,44 +3393,44 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.000521673271312833</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.000522139801452544</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0</v>
+        <v>4.66530139711e-07</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0</v>
+        <v>4.66530139711e-07</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0</v>
+        <v>4.66530139711e-07</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.000521673271312833</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.715194822046709e-07</v>
+        <v>1.196025621379521e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.715194822046709e-07</v>
+        <v>1.196025621379521e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.715194822046709e-07</v>
+        <v>-7.294954816685208e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3443,12 +3443,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Maple syrupUSDT (ERC-4626)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3458,14 +3458,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0</v>
@@ -3483,19 +3483,19 @@
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0</v>
+        <v>1.71712583039288e-07</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0</v>
+        <v>1.71712583039288e-07</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0</v>
+        <v>-1.71712583039288e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3508,12 +3508,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>Maple syrupUSDT (ERC-4626)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
@@ -3573,12 +3573,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3638,12 +3638,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="M45" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" s="6" t="n">
         <v>0</v>
@@ -3698,21 +3698,17 @@
       <c r="R45" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3750,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" s="6" t="n">
         <v>0</v>
@@ -3767,17 +3763,21 @@
       <c r="R46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -3800,13 +3800,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>1435964.694856968</v>
+        <v>0</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>1435964.694856968</v>
+        <v>0</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0</v>
@@ -3824,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>1435964.694856968</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -3837,12 +3837,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3865,13 +3865,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0</v>
+        <v>1435964.694856997</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0</v>
+        <v>1435964.694856997</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
@@ -3889,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0</v>
+        <v>1435964.694856997</v>
       </c>
       <c r="Q48" s="6" t="n">
         <v>0</v>
@@ -3902,12 +3902,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S64</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>RLUSD raw (ALM idle — $251.7M as of 2026-08)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3945,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3962,26 +3962,22 @@
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3990,13 +3986,13 @@
         </is>
       </c>
       <c r="E50" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>146550618.2104181</v>
+        <v>0</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>81380618.21041812</v>
+        <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
         <v>0</v>
@@ -4011,10 +4007,10 @@
         <v>0</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>67882687.2736806</v>
+        <v>0</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50" s="6" t="n">
         <v>0</v>
@@ -4026,36 +4022,32 @@
         <v>0</v>
       </c>
       <c r="Q50" s="6" t="n">
-        <v>67882687.2736806</v>
+        <v>0</v>
       </c>
       <c r="R50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
@@ -4083,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>0</v>
@@ -4100,22 +4092,26 @@
       <c r="R51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4124,13 +4120,13 @@
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>90000000</v>
+        <v>146550618.2104181</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0</v>
+        <v>81380618.21041812</v>
       </c>
       <c r="H52" s="6" t="n">
         <v>0</v>
@@ -4145,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>90000000</v>
+        <v>67882687.2736806</v>
       </c>
       <c r="M52" s="7" t="n">
         <v>0</v>
@@ -4160,7 +4156,7 @@
         <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>90000000</v>
+        <v>67882687.2736806</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>0</v>
@@ -4174,32 +4170,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>100304256.5863323</v>
+        <v>0</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>10404256.58633234</v>
+        <v>0</v>
       </c>
       <c r="H53" s="6" t="n">
         <v>0</v>
@@ -4214,10 +4210,10 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>90246808.55287774</v>
+        <v>0</v>
       </c>
       <c r="M53" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N53" s="6" t="n">
         <v>0</v>
@@ -4229,31 +4225,27 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>90246808.55287774</v>
+        <v>0</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>USDS raw (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4262,13 +4254,13 @@
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>99990828.81481861</v>
+        <v>90000000</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>10090828.81481861</v>
+        <v>0</v>
       </c>
       <c r="H54" s="6" t="n">
         <v>0</v>
@@ -4283,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>90236360.96049395</v>
+        <v>90000000</v>
       </c>
       <c r="M54" s="7" t="n">
         <v>0</v>
@@ -4298,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="Q54" s="6" t="n">
-        <v>90236360.96049395</v>
+        <v>90000000</v>
       </c>
       <c r="R54" s="6" t="n">
         <v>0</v>
@@ -4312,17 +4304,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>USDS raw (Optimism — POL)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4331,13 +4323,13 @@
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>0</v>
+        <v>89900000</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0</v>
+        <v>100304256.5863323</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0</v>
+        <v>10404256.58633234</v>
       </c>
       <c r="H55" s="6" t="n">
         <v>0</v>
@@ -4352,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0</v>
+        <v>90246808.55287774</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55" s="6" t="n">
         <v>0</v>
@@ -4367,178 +4359,260 @@
         <v>0</v>
       </c>
       <c r="Q55" s="6" t="n">
-        <v>0</v>
+        <v>90246808.55287774</v>
       </c>
       <c r="R55" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>S52</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>USDS raw (Unichain — POL)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>unichain</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>99990828.81481861</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>10090828.81481861</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>90236360.96049395</v>
+      </c>
+      <c r="M56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v>90236360.96049395</v>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>S55</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>avalanche_c</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="inlineStr">
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr">
         <is>
           <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>Position-only venues (PnL aggregated at prime level)</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Pricing cat.</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Position SoM</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Position EoM</t>
         </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>S56</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="n">
-        <v>303545287.192935</v>
-      </c>
-      <c r="F60" s="6" t="n">
-        <v>317193040.533521</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>S57</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="n">
-        <v>1270360913.25412</v>
-      </c>
-      <c r="F61" s="6" t="n">
-        <v>863439216.480082</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
+          <t>Spark Savings V2 — spUSDC vault</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4552,51 +4626,107 @@
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>773533.783718</v>
+        <v>303545287.192935</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>797030.383413</v>
+        <v>317193040.533521</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDT vault</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>1270360913.25412</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>863439216.480082</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>S59</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spPYUSD vault</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>773533.783718</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>797030.383413</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>S60</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>avalanche_c</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="E63" s="6" t="n">
+      <c r="E65" s="6" t="n">
         <v>25647247.422478</v>
       </c>
-      <c r="F63" s="6" t="n">
+      <c r="F65" s="6" t="n">
         <v>19103797.28946</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr"/>
-      <c r="B64" s="5" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" s="9" t="n">
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4677,17 +4807,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Base rate (BR = SSR (+) spread; 30bps, 20bps from 2026-07-23), period avg</t>
+          <t>Base rate (BR_apr = apy_to_apr(SSR,12) + spread; 30bps, 20bps from 2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reference rate (tbill_3m), period avg</t>
+          <t>Reference rate (tbill_3m→sofr@2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
@@ -4701,7 +4831,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.03831000088868387</v>
+        <v>0.03814532325251488</v>
       </c>
     </row>
     <row r="11">
@@ -4711,7 +4841,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.03883709630935921</v>
+        <v>0.0383263012019912</v>
       </c>
     </row>
     <row r="12">
@@ -4721,7 +4851,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-2.709079563233819</v>
+        <v>-0.9301611152191143</v>
       </c>
     </row>
     <row r="13">
@@ -4731,7 +4861,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>63153.86653210641</v>
+        <v>22520.05980807343</v>
       </c>
     </row>
     <row r="15">
@@ -4741,7 +4871,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9288441.718268225</v>
+        <v>9301671.608599406</v>
       </c>
     </row>
     <row r="16">
@@ -4751,7 +4881,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>9225287.851736117</v>
+        <v>9279151.548791332</v>
       </c>
     </row>
     <row r="17">
@@ -4761,7 +4891,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>63153.86653210641</v>
+        <v>22520.05980807343</v>
       </c>
     </row>
     <row r="19">
@@ -4791,7 +4921,7 @@
         <v>1000000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3090106.928915537</v>
+        <v>3135232.048151908</v>
       </c>
     </row>
     <row r="21">
@@ -4804,7 +4934,7 @@
         <v>1945662385.958666</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>6135180.922820581</v>
+        <v>6143919.500639424</v>
       </c>
     </row>
     <row r="23">
@@ -4826,7 +4956,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>9054205.487267924</v>
+        <v>9107813.391973251</v>
       </c>
     </row>
     <row r="25">
@@ -4846,7 +4976,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>9075246.988098558</v>
+        <v>9128854.892803885</v>
       </c>
     </row>
     <row r="28">
@@ -4863,7 +4993,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>11790351.17991679</v>
+        <v>11847868.39685765</v>
       </c>
     </row>
     <row r="31">
@@ -4873,7 +5003,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>9054205.487267924</v>
+        <v>9107813.391973251</v>
       </c>
     </row>
     <row r="32">
@@ -4883,7 +5013,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-2736145.692648868</v>
+        <v>-2740055.004884402</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -4900,7 +5030,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>171082.3644681933</v>
+        <v>171338.1568180806</v>
       </c>
     </row>
     <row r="37">
@@ -4991,14 +5121,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>subsidised_apy = ref_rate + (base_apy − ref_rate) × min(T, 24) / 24, applied to first cap_usd of utilized; excess at full base_apy</t>
+          <t>subsidised_apr = ref_rate + (base_apr − ref_rate) × min(T, 24) / 24, applied to first cap_usd of utilized; excess at full base_apr</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Base rate composition: base_apy = (1 + SSR)(1 + spread) − 1 (multiplicative; spread 30bps, 20bps from 2026-07-23)</t>
+          <t>Base rate composition: base_apr = apy_to_apr(SSR, n=12) + spread (nominal; spread 30bps, 20bps from 2026-07-23). Daily charge = utilized_d x base_apr / 365 — no intra-month compounding.</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5426,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+spread)−1 (multiplicative; spread 30bps, 20bps from 2026-07-23). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apr = apy_to_apr(SSR, n=12) + spread (nominal; spread 30bps, 20bps from 2026-07-23). sub_apr applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apr.</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5477,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>base APY</t>
+          <t>base APR</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -5357,12 +5487,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>ref_rate APY</t>
+          <t>ref_rate APR</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>sub APY</t>
+          <t>sub APR</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5407,7 +5537,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
@@ -5416,13 +5546,13 @@
         <v>0.0378</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.03807250088868387</v>
+        <v>0.03792902444031523</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>332216.9641822214</v>
+        <v>334082.6434197158</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>425433.9582668049</v>
+        <v>427432.4101098824</v>
       </c>
     </row>
     <row r="7">
@@ -5456,7 +5586,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
@@ -5465,13 +5595,13 @@
         <v>0.0377</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.03799333422201721</v>
+        <v>0.03784985777364856</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>335515.3748822335</v>
+        <v>337378.1242832829</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>430588.0680321992</v>
+        <v>432586.2331834913</v>
       </c>
     </row>
     <row r="8">
@@ -5505,7 +5635,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K8" t="n">
         <v>5</v>
@@ -5514,13 +5644,13 @@
         <v>0.0378</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.03807250088868387</v>
+        <v>0.03792902444031523</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>335065.4896588066</v>
+        <v>336935.2261623961</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>429834.173678943</v>
+        <v>431838.8929206975</v>
       </c>
     </row>
     <row r="9">
@@ -5554,7 +5684,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
@@ -5563,13 +5693,13 @@
         <v>0.0378</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.03807250088868387</v>
+        <v>0.03792902444031523</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>329393.2853526921</v>
+        <v>331254.9427141412</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>420609.2671465119</v>
+        <v>422600.8469935819</v>
       </c>
     </row>
     <row r="10">
@@ -5603,7 +5733,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K10" t="n">
         <v>5</v>
@@ -5612,13 +5742,13 @@
         <v>0.0378</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.03807250088868387</v>
+        <v>0.03792902444031523</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>322751.4626277998</v>
+        <v>324603.6597817227</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>403087.5532993731</v>
+        <v>405054.1762850403</v>
       </c>
     </row>
     <row r="11">
@@ -5652,7 +5782,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K11" t="n">
         <v>5</v>
@@ -5661,13 +5791,13 @@
         <v>0.0378</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.03807250088868387</v>
+        <v>0.03792902444031523</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>323389.2389220453</v>
+        <v>325242.3444856546</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>407154.8427349417</v>
+        <v>409127.2589198138</v>
       </c>
     </row>
     <row r="12">
@@ -5701,7 +5831,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K12" t="n">
         <v>5</v>
@@ -5710,13 +5840,13 @@
         <v>0.0378</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.03807250088868387</v>
+        <v>0.03792902444031523</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>325841.8410263725</v>
+        <v>327698.4399269537</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>411782.3518007405</v>
+        <v>413761.3591275181</v>
       </c>
     </row>
     <row r="13">
@@ -5750,7 +5880,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K13" t="n">
         <v>5</v>
@@ -5759,13 +5889,13 @@
         <v>0.038</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.03823083422201721</v>
+        <v>0.03808735777364856</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>320013.1016180831</v>
+        <v>321876.7019438379</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>409304.0719372209</v>
+        <v>411294.8528795654</v>
       </c>
     </row>
     <row r="14">
@@ -5799,7 +5929,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K14" t="n">
         <v>5</v>
@@ -5808,13 +5938,13 @@
         <v>0.0379</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.03815166755535054</v>
+        <v>0.0380081911069819</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>317834.1303211373</v>
+        <v>319686.9673334853</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>406446.3261341003</v>
+        <v>408425.376957997</v>
       </c>
     </row>
     <row r="15">
@@ -5848,7 +5978,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K15" t="n">
         <v>5</v>
@@ -5857,13 +5987,13 @@
         <v>0.0379</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.03815166755535054</v>
+        <v>0.0380081911069819</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>316763.1377641822</v>
+        <v>318614.4493200001</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>405841.8653905716</v>
+        <v>407820.055257422</v>
       </c>
     </row>
     <row r="16">
@@ -5897,7 +6027,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K16" t="n">
         <v>5</v>
@@ -5906,13 +6036,13 @@
         <v>0.0378</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.03807250088868387</v>
+        <v>0.03792902444031523</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>315907.7645221049</v>
+        <v>317750.2139295118</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>404523.9031277228</v>
+        <v>406492.571962552</v>
       </c>
     </row>
     <row r="17">
@@ -5946,7 +6076,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K17" t="n">
         <v>5</v>
@@ -5955,13 +6085,13 @@
         <v>0.0378</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.03807250088868387</v>
+        <v>0.03792902444031523</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>319558.7122369504</v>
+        <v>321406.3618317878</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>406842.0022293216</v>
+        <v>408813.9728232425</v>
       </c>
     </row>
     <row r="18">
@@ -5995,7 +6125,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K18" t="n">
         <v>5</v>
@@ -6004,13 +6134,13 @@
         <v>0.0378</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.03807250088868387</v>
+        <v>0.03792902444031523</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>313577.4860457859</v>
+        <v>315416.616346542</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>400489.3307295096</v>
+        <v>402452.252965288</v>
       </c>
     </row>
     <row r="19">
@@ -6044,7 +6174,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K19" t="n">
         <v>5</v>
@@ -6053,13 +6183,13 @@
         <v>0.0378</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.03807250088868387</v>
+        <v>0.03792902444031523</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>314599.7205365335</v>
+        <v>316440.3068458016</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>401100.4654462736</v>
+        <v>403064.258145099</v>
       </c>
     </row>
     <row r="20">
@@ -6093,7 +6223,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K20" t="n">
         <v>5</v>
@@ -6102,13 +6232,13 @@
         <v>0.0379</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0.03815166755535054</v>
+        <v>0.0380081911069819</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>315926.0497723278</v>
+        <v>317776.1690310235</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>403573.5341132453</v>
+        <v>405548.4931072599</v>
       </c>
     </row>
     <row r="21">
@@ -6142,7 +6272,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K21" t="n">
         <v>5</v>
@@ -6151,13 +6281,13 @@
         <v>0.0379</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.03815166755535054</v>
+        <v>0.0380081911069819</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>287288.6747512537</v>
+        <v>289098.0046781763</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>374955.1392312443</v>
+        <v>376889.3359276393</v>
       </c>
     </row>
     <row r="22">
@@ -6191,7 +6321,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K22" t="n">
         <v>5</v>
@@ -6200,13 +6330,13 @@
         <v>0.0383</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.0384683342220172</v>
+        <v>0.03832485777364857</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>287658.915191066</v>
+        <v>289499.5067949062</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>376650.5013859501</v>
+        <v>378617.8471818783</v>
       </c>
     </row>
     <row r="23">
@@ -6240,7 +6370,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K23" t="n">
         <v>5</v>
@@ -6249,13 +6379,13 @@
         <v>0.0383</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.0384683342220172</v>
+        <v>0.03832485777364857</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>285068.9989912522</v>
+        <v>286905.901676291</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>373258.4002760279</v>
+        <v>375220.9145698551</v>
       </c>
     </row>
     <row r="24">
@@ -6289,7 +6419,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K24" t="n">
         <v>5</v>
@@ -6298,13 +6428,13 @@
         <v>0.0383</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.0384683342220172</v>
+        <v>0.03832485777364857</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>284931.8584873506</v>
+        <v>286768.5658378133</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>372918.634642558</v>
+        <v>374880.6649949229</v>
       </c>
     </row>
     <row r="25">
@@ -6338,7 +6468,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K25" t="n">
         <v>5</v>
@@ -6347,13 +6477,13 @@
         <v>0.0383</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.0384683342220172</v>
+        <v>0.03832485777364857</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>297422.7060859893</v>
+        <v>299277.2046385594</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>374939.1809647587</v>
+        <v>376904.0892601696</v>
       </c>
     </row>
     <row r="26">
@@ -6387,7 +6517,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K26" t="n">
         <v>5</v>
@@ -6396,13 +6526,13 @@
         <v>0.0383</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.0384683342220172</v>
+        <v>0.03832485777364857</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>297131.8945123657</v>
+        <v>298985.9788506528</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>374598.8315564164</v>
+        <v>376563.2550788715</v>
       </c>
     </row>
     <row r="27">
@@ -6436,7 +6566,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K27" t="n">
         <v>5</v>
@@ -6445,13 +6575,13 @@
         <v>0.0385</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.03862666755535054</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>297502.0380628955</v>
+        <v>299197.1155084428</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>373374.436278404</v>
+        <v>375177.5817441856</v>
       </c>
     </row>
     <row r="28">
@@ -6485,7 +6615,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K28" t="n">
         <v>5</v>
@@ -6494,13 +6624,13 @@
         <v>0.0385</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0.03862666755535054</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>297138.5780364425</v>
+        <v>298833.137791678</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>372367.0470202919</v>
+        <v>374168.7576222062</v>
       </c>
     </row>
     <row r="29">
@@ -6534,7 +6664,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K29" t="n">
         <v>5</v>
@@ -6543,13 +6673,13 @@
         <v>0.0385</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.03862666755535054</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>293822.8688674631</v>
+        <v>295512.7059286229</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>369630.016398093</v>
+        <v>371427.828540388</v>
       </c>
     </row>
     <row r="30">
@@ -6583,7 +6713,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K30" t="n">
         <v>5</v>
@@ -6592,13 +6722,13 @@
         <v>0.0384</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.03854750088868387</v>
+        <v>0.03840402444031523</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>295094.5855362514</v>
+        <v>296953.4914013887</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>376647.9380003725</v>
+        <v>378623.0034907695</v>
       </c>
     </row>
     <row r="31">
@@ -6632,7 +6762,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K31" t="n">
         <v>5</v>
@@ -6641,13 +6771,13 @@
         <v>0.0383</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.0384683342220172</v>
+        <v>0.03832485777364857</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>296177.3275713244</v>
+        <v>298030.0522826335</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>378631.8678127691</v>
+        <v>380602.0357462881</v>
       </c>
     </row>
     <row r="32">
@@ -6681,7 +6811,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K32" t="n">
         <v>5</v>
@@ -6690,13 +6820,13 @@
         <v>0.0383</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.0384683342220172</v>
+        <v>0.03832485777364857</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>294756.6580930781</v>
+        <v>296607.3592893603</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>376969.4893143523</v>
+        <v>378937.2894572461</v>
       </c>
     </row>
     <row r="33">
@@ -6730,7 +6860,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K33" t="n">
         <v>5</v>
@@ -6739,13 +6869,13 @@
         <v>0.0383</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.0384683342220172</v>
+        <v>0.03832485777364857</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>294757.0176235051</v>
+        <v>296607.7193318804</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>376940.4234585383</v>
+        <v>378908.1822017985</v>
       </c>
     </row>
     <row r="34">
@@ -6779,7 +6909,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K34" t="n">
         <v>5</v>
@@ -6788,13 +6918,13 @@
         <v>0.0387</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>0.03878500088868388</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>294087.6133054312</v>
+        <v>295359.5636821942</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>375552.3690651191</v>
+        <v>376940.3528753953</v>
       </c>
     </row>
     <row r="35">
@@ -6828,7 +6958,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K35" t="n">
         <v>5</v>
@@ -6837,13 +6967,13 @@
         <v>0.0387</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.03878500088868388</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>284094.3571511732</v>
+        <v>285352.0737428749</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>376305.1904444174</v>
+        <v>377694.2465275881</v>
       </c>
     </row>
     <row r="37">
@@ -6865,10 +6995,10 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" s="12" t="n">
-        <v>9225287.851736117</v>
+        <v>9279151.548791332</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>11790351.17991679</v>
+        <v>11847868.39685765</v>
       </c>
     </row>
   </sheetData>
